--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-18T07:45:31</t>
+    <t xml:space="preserve">2026-05-18T10:22:39</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -351,6 +351,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
   </si>
   <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
     <t xml:space="preserve">Appsflyer</t>
   </si>
   <si>
@@ -378,9 +393,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
     <t xml:space="preserve">Torq</t>
   </si>
   <si>
@@ -540,6 +552,51 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4408746535</t>
   </si>
   <si>
+    <t xml:space="preserve">Deepdub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest acq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4414943772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 234407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-234407-at-experis-israel-4412205944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Engineer</t>
   </si>
   <si>
@@ -549,49 +606,25 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deepdub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest acq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4414943772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 234407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-234407-at-experis-israel-4412205944</t>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPlus - Payment Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-payplus-payment-gateway-4413875202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SailPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
   </si>
   <si>
     <t xml:space="preserve">eko</t>
@@ -600,25 +633,256 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4414506870</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4405650446</t>
+  </si>
+  <si>
     <t xml:space="preserve">Play Perfect</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
   </si>
   <si>
-    <t xml:space="preserve">Autodesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4413282456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4416073307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freightos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Team Lead</t>
   </si>
   <si>
-    <t xml:space="preserve">Cycode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cycode-4413964734</t>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (Azure &amp; AI Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-ai-focus-at-kpmg-israel-4413043824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-allpha-innovation-4413893764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4415415831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
   </si>
   <si>
     <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
@@ -627,271 +891,298 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-unity-south-apac-sea-anz-ind-subcont-4413091861</t>
   </si>
   <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI21 Labs</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ai21-labs-4413404972</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SailPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4413282456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure DevOps / Infrastructure Engineer | Leading company! (5433)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-engineer-leading-company%21-5433-at-ingima-4416022270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4416073307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freightos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4415415831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (Azure &amp; AI Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-ai-focus-at-kpmg-israel-4413043824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-allpha-innovation-4413893764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412250454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-solaredge-technologies-4413102721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Sub contractor (for 7 months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Semiconductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-for-7-months-at-samsung-semiconductor-4416091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4410353746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Infrastructure Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">LayerX Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-confidential-careers-4412213973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-kela-technologies-4410027133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playermaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4414599051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coralogix</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-coralogix-4343793999</t>
   </si>
   <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer - Tactical Munitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-tactical-munitions-at-kela-technologies-4410014250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413098703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
   </si>
   <si>
     <t xml:space="preserve">Teads</t>
@@ -900,297 +1191,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412250454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-solaredge-technologies-4413102721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer (Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-platform-at-toluna-4400400595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer - ARS Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-ars-team-at-cyberark-4372086494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-cloud-at-palo-alto-networks-4383006183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LayerX Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-confidential-careers-4412213973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-kela-technologies-4410027133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playermaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4414599051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer - Tactical Munitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-tactical-munitions-at-kela-technologies-4410014250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413098703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unity</t>
   </si>
   <si>
@@ -1329,10 +1329,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6%</t>
+    <t xml:space="preserve">60.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1371,6 +1371,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Kubernetes, CI/CD, Terraform/IaC, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-gini-apps-4404896510</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
@@ -1491,6 +1500,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
   </si>
   <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
   </si>
   <si>
@@ -1566,30 +1584,9 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4414971429</t>
   </si>
   <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1602,19 +1599,22 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1766,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -1774,7 +1774,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1782,7 +1782,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9">
@@ -1790,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -1870,7 +1870,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -1905,12 +1905,12 @@
         <v>442</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B3" s="3">
         <v>10</v>
@@ -1921,12 +1921,12 @@
         <v>447</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1956,15 +1956,15 @@
         <v>415</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1972,7 +1972,7 @@
         <v>424</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1980,20 +1980,20 @@
         <v>426</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -2001,23 +2001,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>220</v>
+        <v>421</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>421</v>
+        <v>228</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B9" s="3">
         <v>10</v>
@@ -2025,18 +2025,18 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -2044,12 +2044,12 @@
         <v>418</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -2057,15 +2057,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>420</v>
+        <v>530</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>531</v>
+        <v>417</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>417</v>
+        <v>531</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2115,10 +2115,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>17.3</v>
+        <v>15.2</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>535</v>
@@ -2133,7 +2133,7 @@
         <v>83</v>
       </c>
       <c r="C3" s="3">
-        <v>35.7</v>
+        <v>34.5</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>535</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>535</v>
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>535</v>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>45.5</v>
+        <v>33.0</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>535</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.1</v>
+        <v>26.0</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>535</v>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.0</v>
+        <v>15.5</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>535</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>535</v>
@@ -2237,7 +2237,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -2985,19 +2985,19 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>112</v>
@@ -3009,15 +3009,15 @@
         <v>113</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="J24" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>115</v>
@@ -3026,7 +3026,7 @@
         <v>116</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
@@ -3041,47 +3041,47 @@
         <v>118</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="J26" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>124</v>
@@ -3095,12 +3095,14 @@
       <c r="E27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
@@ -3111,28 +3113,26 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>130</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
@@ -3143,28 +3143,28 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
@@ -3175,10 +3175,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>56</v>
@@ -3187,16 +3187,16 @@
         <v>56</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
@@ -3242,7 +3242,7 @@
         <v>140</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>55</v>
@@ -3254,13 +3254,13 @@
         <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
@@ -3271,28 +3271,28 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
@@ -3303,13 +3303,13 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>56</v>
@@ -3318,13 +3318,13 @@
         <v>57</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>41</v>
@@ -3335,28 +3335,28 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>41</v>
@@ -3367,13 +3367,13 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>56</v>
@@ -3382,13 +3382,13 @@
         <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>41</v>
@@ -3399,21 +3399,23 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
@@ -3421,10 +3423,10 @@
         <v>160</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -3435,10 +3437,10 @@
         <v>162</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>57</v>
@@ -3448,7 +3450,7 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>44</v>
@@ -3459,13 +3461,13 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>56</v>
@@ -3475,10 +3477,10 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>44</v>
@@ -3492,10 +3494,10 @@
         <v>90</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>56</v>
@@ -3508,7 +3510,7 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>44</v>
@@ -3522,7 +3524,7 @@
         <v>90</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>71</v>
@@ -3538,13 +3540,13 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -3552,10 +3554,10 @@
         <v>90</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>56</v>
@@ -3568,24 +3570,24 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J42" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>173</v>
+        <v>90</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>56</v>
@@ -3598,37 +3600,37 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>44</v>
@@ -3639,19 +3641,19 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="D45" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3721,7 +3723,7 @@
         <v>190</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="J47" s="3">
         <v>1</v>
@@ -3729,13 +3731,13 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>56</v>
@@ -3748,13 +3750,13 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3762,10 +3764,10 @@
         <v>90</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
@@ -3778,10 +3780,10 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3792,10 +3794,10 @@
         <v>90</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
@@ -3808,7 +3810,7 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>44</v>
@@ -3819,26 +3821,26 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>197</v>
+        <v>90</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>44</v>
@@ -3849,13 +3851,13 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
@@ -3868,7 +3870,7 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>44</v>
@@ -3879,59 +3881,59 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>90</v>
+        <v>204</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>204</v>
+        <v>90</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>56</v>
+        <v>209</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="J54" s="3">
         <v>1</v>
@@ -3942,13 +3944,13 @@
         <v>90</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>209</v>
+        <v>56</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>57</v>
@@ -3958,37 +3960,37 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>44</v>
@@ -3999,48 +4001,46 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>213</v>
+        <v>90</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="3"/>
+      <c r="G57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="I57" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="D58" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>57</v>
@@ -4055,39 +4055,37 @@
         <v>221</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>129</v>
+        <v>224</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="J59" s="3">
         <v>1</v>
@@ -4095,43 +4093,45 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>56</v>
@@ -4144,7 +4144,7 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>44</v>
@@ -4155,16 +4155,16 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>57</v>
@@ -4174,10 +4174,10 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -4185,26 +4185,28 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>44</v>
@@ -4215,28 +4217,26 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>215</v>
+        <v>71</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>238</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>44</v>
@@ -4247,13 +4247,13 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>56</v>
@@ -4261,12 +4261,14 @@
       <c r="E65" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>44</v>
@@ -4277,88 +4279,86 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>63</v>
+        <v>246</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J67" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>250</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>44</v>
@@ -4369,16 +4369,16 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>90</v>
+        <v>253</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>56</v>
+        <v>209</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>57</v>
@@ -4388,27 +4388,27 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>182</v>
+        <v>256</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>57</v>
@@ -4418,27 +4418,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>257</v>
+        <v>90</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>227</v>
+        <v>56</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>57</v>
@@ -4448,27 +4448,27 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>261</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>71</v>
+        <v>262</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>57</v>
@@ -4478,7 +4478,7 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>44</v>
@@ -4489,46 +4489,46 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>90</v>
+        <v>267</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>57</v>
@@ -4538,7 +4538,7 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>44</v>
@@ -4549,16 +4549,16 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>270</v>
+        <v>169</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>57</v>
@@ -4568,7 +4568,7 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>44</v>
@@ -4579,13 +4579,13 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
@@ -4598,7 +4598,7 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>44</v>
@@ -4609,26 +4609,26 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>44</v>
@@ -4639,26 +4639,26 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>44</v>
@@ -4669,26 +4669,26 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>275</v>
+        <v>63</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>282</v>
+        <v>169</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>44</v>
@@ -4699,26 +4699,26 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>63</v>
+        <v>285</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>44</v>
@@ -4729,26 +4729,26 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>286</v>
+        <v>53</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>44</v>
@@ -4759,56 +4759,56 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>44</v>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>71</v>
@@ -4833,12 +4833,14 @@
       <c r="E84" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>44</v>
@@ -4849,13 +4851,13 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>56</v>
@@ -4868,24 +4870,24 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>56</v>
@@ -4893,14 +4895,12 @@
       <c r="E86" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>301</v>
-      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>44</v>
@@ -4911,26 +4911,26 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>294</v>
+        <v>168</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>44</v>
@@ -4941,56 +4941,56 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J88" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>44</v>
@@ -5001,56 +5001,56 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>165</v>
+        <v>314</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>44</v>
@@ -5061,16 +5061,16 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>318</v>
+        <v>180</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>57</v>
@@ -5080,7 +5080,7 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>44</v>
@@ -5091,49 +5091,49 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>71</v>
+        <v>196</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>323</v>
+        <v>90</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>325</v>
+        <v>219</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
@@ -5143,24 +5143,24 @@
         <v>326</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="C95" s="3" t="s">
-        <v>226</v>
+        <v>180</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>227</v>
+        <v>56</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>38</v>
@@ -5170,87 +5170,87 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>334</v>
-      </c>
       <c r="C97" s="3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="D98" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>57</v>
@@ -5260,24 +5260,24 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>339</v>
+        <v>175</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>56</v>
@@ -5290,27 +5290,27 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="C100" s="3" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>57</v>
@@ -5320,27 +5320,27 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>345</v>
+        <v>208</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>37</v>
+        <v>209</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>57</v>
@@ -5350,7 +5350,7 @@
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>44</v>
@@ -5361,46 +5361,46 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>171</v>
+        <v>346</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>165</v>
+        <v>336</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J102" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="D103" s="3" t="s">
-        <v>56</v>
+        <v>224</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>57</v>
@@ -5410,7 +5410,7 @@
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>44</v>
@@ -5421,16 +5421,16 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>227</v>
+        <v>56</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>57</v>
@@ -5440,7 +5440,7 @@
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>44</v>
@@ -5451,16 +5451,16 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>57</v>
@@ -5470,27 +5470,27 @@
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J105" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>357</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>253</v>
+        <v>358</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>57</v>
@@ -5500,30 +5500,30 @@
         <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="J106" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
@@ -5544,43 +5544,43 @@
         <v>362</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>363</v>
+        <v>268</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>364</v>
+        <v>262</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="J108" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>38</v>
@@ -5590,10 +5590,10 @@
         <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="J109" s="3">
         <v>1</v>
@@ -5601,16 +5601,16 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>266</v>
+        <v>169</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>38</v>
@@ -5620,7 +5620,7 @@
         <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>44</v>
@@ -5631,26 +5631,26 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>171</v>
+        <v>369</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>44</v>
@@ -5661,16 +5661,16 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="D112" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>57</v>
@@ -5683,10 +5683,10 @@
         <v>374</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="J112" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5700,7 +5700,7 @@
         <v>377</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>57</v>
@@ -5713,7 +5713,7 @@
         <v>378</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J113" s="3">
         <v>0</v>
@@ -5727,50 +5727,50 @@
         <v>380</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>381</v>
+        <v>196</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J114" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>44</v>
@@ -5784,10 +5784,10 @@
         <v>60</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>56</v>
@@ -5800,7 +5800,7 @@
         <v>22</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>44</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>71</v>
@@ -5830,10 +5830,10 @@
         <v>22</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J117" s="3">
         <v>0</v>
@@ -5841,16 +5841,16 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>38</v>
@@ -5860,42 +5860,40 @@
         <v>22</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="J118" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>392</v>
+        <v>60</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>394</v>
+        <v>169</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>394</v>
+        <v>56</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F119" s="3" t="s">
-        <v>395</v>
-      </c>
+      <c r="F119" s="3"/>
       <c r="G119" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J119" s="3">
         <v>0</v>
@@ -5903,10 +5901,10 @@
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>394</v>
@@ -5915,80 +5913,80 @@
         <v>394</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="J120" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>129</v>
+        <v>394</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="J121" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>394</v>
+        <v>133</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>44</v>
@@ -5999,38 +5997,70 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>394</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H123" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J123" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="I123" s="3" t="s">
+      <c r="I124" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J123" s="3">
+      <c r="J124" s="3">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J123"/>
+  <autoFilter ref="A1:J124"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6154,6 +6184,7 @@
     <hyperlink ref="H121" r:id="rId120"/>
     <hyperlink ref="H122" r:id="rId121"/>
     <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6161,8 +6192,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -6195,13 +6226,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6209,26 +6240,26 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
@@ -6236,10 +6267,10 @@
         <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6247,18 +6278,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6266,18 +6297,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6285,18 +6316,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6304,18 +6335,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6323,7 +6354,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
@@ -6331,7 +6362,7 @@
         <v>182</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>184</v>
@@ -6342,18 +6373,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>296</v>
+        <v>63</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6361,18 +6392,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6380,18 +6411,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6399,18 +6430,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6418,18 +6449,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6437,18 +6468,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>345</v>
+        <v>169</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6456,18 +6487,18 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>376</v>
+        <v>333</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>377</v>
+        <v>219</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6475,18 +6506,18 @@
         <v>22</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>381</v>
+        <v>336</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6494,18 +6525,18 @@
         <v>22</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>71</v>
+        <v>373</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6513,18 +6544,18 @@
         <v>22</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>60</v>
+        <v>375</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>165</v>
+        <v>377</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -6532,30 +6563,68 @@
         <v>22</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>394</v>
+        <v>71</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G22"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6576,6 +6645,8 @@
     <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
     <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6605,7 +6676,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6616,7 +6687,7 @@
         <v>418</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -6632,12 +6703,12 @@
         <v>420</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -6645,7 +6716,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>301</v>
+        <v>228</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
@@ -6656,7 +6727,7 @@
         <v>421</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -6680,7 +6751,7 @@
         <v>424</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -6688,7 +6759,7 @@
         <v>425</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -6696,7 +6767,7 @@
         <v>426</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -6760,7 +6831,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6768,7 +6839,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6776,7 +6847,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6808,7 +6879,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6816,7 +6887,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6824,7 +6895,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6832,7 +6903,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6840,7 +6911,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6848,7 +6919,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -6928,7 +6999,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C5" s="3">
         <v>14.0</v>
@@ -6942,7 +7013,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C6" s="3">
         <v>11.3</v>
@@ -6998,7 +7069,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C10" s="3">
         <v>5.8</v>
@@ -7012,7 +7083,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C11" s="3">
         <v>4.2</v>
@@ -7026,7 +7097,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C12" s="3">
         <v>2.9</v>
@@ -7040,7 +7111,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -7054,7 +7125,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -7068,7 +7139,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -7130,7 +7201,7 @@
         <v>57</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>436</v>
@@ -7141,7 +7212,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>437</v>
@@ -7171,15 +7242,15 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -7192,15 +7263,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -7216,7 +7287,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -7224,7 +7295,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -7232,7 +7303,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -7332,7 +7403,7 @@
         <v>446</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>447</v>
@@ -7358,28 +7429,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="F4" s="3">
-        <v>71</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>44</v>
@@ -7390,28 +7461,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F5" s="3">
+        <v>71</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="F5" s="3">
-        <v>57</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>44</v>
@@ -7422,28 +7493,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="F6" s="3">
+        <v>57</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="F6" s="3">
-        <v>52</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -7454,28 +7525,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="F7" s="3">
+        <v>52</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="F7" s="3">
-        <v>48</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>44</v>
@@ -7486,25 +7557,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>145</v>
+        <v>219</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>469</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>470</v>
@@ -7521,10 +7592,10 @@
         <v>471</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>472</v>
+        <v>148</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>253</v>
+        <v>149</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>442</v>
@@ -7533,13 +7604,13 @@
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -7550,13 +7621,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>476</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>477</v>
+        <v>196</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>442</v>
@@ -7565,13 +7636,13 @@
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7582,25 +7653,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>481</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>482</v>
@@ -7617,10 +7688,10 @@
         <v>483</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>253</v>
+        <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>442</v>
@@ -7632,7 +7703,7 @@
         <v>484</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>485</v>
@@ -7649,25 +7720,25 @@
         <v>486</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>487</v>
+        <v>275</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>488</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>489</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7678,28 +7749,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>491</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F14" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>492</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7710,28 +7781,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F15" s="3">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="F15" s="3">
-        <v>36</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7742,28 +7813,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F16" s="3">
+        <v>37</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="F16" s="3">
-        <v>36</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7774,28 +7845,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F17" s="3">
+        <v>36</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="F17" s="3">
-        <v>34</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>505</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7806,28 +7877,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F18" s="3">
+        <v>36</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="F18" s="3">
-        <v>34</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7838,28 +7909,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F19" s="3">
+        <v>34</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="F19" s="3">
-        <v>32</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>44</v>
@@ -7870,28 +7941,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>450</v>
+        <v>512</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>184</v>
+        <v>514</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>517</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -7902,28 +7973,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F21" s="3">
+        <v>32</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="F21" s="3">
-        <v>26</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-18T10:22:39</t>
+    <t xml:space="preserve">2026-05-19T05:39:50</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -252,6 +252,18 @@
     <t xml:space="preserve">https://www.payoneer.com/careers/position/7709743/?gh_jid=7709743</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Crossplane</t>
   </si>
   <si>
@@ -525,475 +537,484 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4414226464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4408746535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deepdub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4414506870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFTECH-IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Sub contractor (for 7 months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Semiconductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-for-7-months-at-samsung-semiconductor-4416091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 234407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-234407-at-experis-israel-4412205944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (100656)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-100656-at-elad-software-systems-4416239061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cycode-4413964734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SailPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4408668742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4416466723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freightos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-allpha-innovation-4413893764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4415415831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placer.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-placer-ai-4375474671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4414226464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4408746535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deepdub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest acq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4414943772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 234407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-234407-at-experis-israel-4412205944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFTECH-IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PayPlus - Payment Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-payplus-payment-gateway-4413875202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SailPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4414506870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autodesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4405650446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4413282456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4416073307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freightos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (Azure &amp; AI Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-ai-focus-at-kpmg-israel-4413043824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-allpha-innovation-4413893764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4415415831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-unity-south-apac-sea-anz-ind-subcont-4413091861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI21 Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ai21-labs-4413404972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
   </si>
   <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior HPC DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">NVIDIA AI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412250454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-solaredge-technologies-4413102721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Sub contractor (for 7 months)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-for-7-months-at-samsung-semiconductor-4416091431</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellular DevOps SW Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cellular-devops-sw-engineer-at-apple-4414170146</t>
   </si>
   <si>
     <t xml:space="preserve">Dialog</t>
@@ -1020,12 +1041,6 @@
     <t xml:space="preserve">Infrastructure Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-confidential-careers-4412213973</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medulla</t>
   </si>
   <si>
@@ -1035,21 +1050,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-kela-technologies-4410027133</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
@@ -1074,12 +1089,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
   </si>
   <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4414599051</t>
-  </si>
-  <si>
     <t xml:space="preserve">Uvision Group</t>
   </si>
   <si>
@@ -1101,100 +1110,91 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22490 - System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coralogix</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-coralogix-4343793999</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer - Tactical Munitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-tactical-munitions-at-kela-technologies-4410014250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413098703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
+    <t xml:space="preserve">Software Engineering Manager - SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipalti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Database Reliability Engineer</t>
@@ -1329,10 +1329,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8%</t>
+    <t xml:space="preserve">63.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1371,15 +1371,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Kubernetes, CI/CD, Terraform/IaC, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-gini-apps-4404896510</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
@@ -1545,18 +1536,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer New Window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kramer Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer%0Anew-window-at-kramer-europe-4399396097</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tier II III UC Support Engineer</t>
   </si>
   <si>
@@ -1584,9 +1563,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4414971429</t>
   </si>
   <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1611,10 +1611,10 @@
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
     <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1766,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -1774,7 +1774,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1782,7 +1782,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -1790,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -1862,7 +1862,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -1870,7 +1870,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1910,10 +1910,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1921,12 +1921,12 @@
         <v>447</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1964,7 +1964,7 @@
         <v>523</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1980,7 +1980,7 @@
         <v>426</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1988,7 +1988,7 @@
         <v>524</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -1996,12 +1996,12 @@
         <v>525</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>233</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>421</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2028,7 +2028,7 @@
         <v>527</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2036,7 +2036,7 @@
         <v>528</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         <v>418</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2052,7 +2052,7 @@
         <v>529</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -2060,12 +2060,12 @@
         <v>530</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>417</v>
+        <v>531</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>531</v>
+        <v>420</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -2115,10 +2115,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>535</v>
@@ -2133,7 +2133,7 @@
         <v>83</v>
       </c>
       <c r="C3" s="3">
-        <v>34.5</v>
+        <v>38.6</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>535</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>535</v>
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>535</v>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.0</v>
+        <v>84.2</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>535</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>26.0</v>
+        <v>22.9</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>535</v>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.5</v>
+        <v>16.2</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>535</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>535</v>
@@ -2238,7 +2238,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2310,7 +2310,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2342,7 +2342,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2374,7 +2374,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2404,7 +2404,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2436,7 +2436,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2468,7 +2468,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2500,7 +2500,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2532,7 +2532,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2564,7 +2564,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2596,7 +2596,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2628,12 +2628,12 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>70</v>
@@ -2645,27 +2645,27 @@
         <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="J13" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>70</v>
@@ -2680,30 +2680,30 @@
         <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>56</v>
@@ -2712,62 +2712,62 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>56</v>
@@ -2776,30 +2776,30 @@
         <v>57</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>56</v>
@@ -2808,30 +2808,30 @@
         <v>57</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>56</v>
@@ -2852,7 +2852,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2860,10 +2860,10 @@
         <v>100</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>56</v>
@@ -2872,62 +2872,62 @@
         <v>57</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>56</v>
@@ -2936,7 +2936,7 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
@@ -2945,18 +2945,18 @@
         <v>107</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>56</v>
@@ -2968,27 +2968,27 @@
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J23" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>56</v>
@@ -2997,7 +2997,7 @@
         <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>112</v>
@@ -3009,111 +3009,111 @@
         <v>113</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J25" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="J27" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>128</v>
@@ -3127,90 +3127,90 @@
       <c r="E28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>56</v>
@@ -3219,42 +3219,42 @@
         <v>56</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
@@ -3266,7 +3266,7 @@
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -3274,7 +3274,7 @@
         <v>144</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>55</v>
@@ -3286,62 +3286,62 @@
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>56</v>
@@ -3350,62 +3350,62 @@
         <v>57</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>56</v>
@@ -3414,38 +3414,40 @@
         <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
@@ -3453,10 +3455,10 @@
         <v>164</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -3467,10 +3469,10 @@
         <v>166</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>57</v>
@@ -3480,24 +3482,24 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>169</v>
+        <v>56</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>56</v>
@@ -3507,30 +3509,30 @@
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J40" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>57</v>
@@ -3540,21 +3542,21 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J41" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>71</v>
@@ -3570,27 +3572,27 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>57</v>
@@ -3600,54 +3602,54 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>56</v>
@@ -3660,30 +3662,30 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3696,18 +3698,18 @@
         <v>44</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>56</v>
@@ -3720,24 +3722,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>192</v>
+        <v>94</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>56</v>
@@ -3750,24 +3752,24 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
@@ -3780,24 +3782,24 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
@@ -3813,24 +3815,24 @@
         <v>199</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>57</v>
@@ -3840,24 +3842,24 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
@@ -3870,57 +3872,57 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>90</v>
+        <v>212</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>57</v>
@@ -3930,84 +3932,84 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
@@ -4020,59 +4022,57 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>220</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>224</v>
+        <v>56</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>57</v>
@@ -4082,42 +4082,40 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>228</v>
-      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
@@ -4125,46 +4123,48 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>233</v>
+        <v>94</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>57</v>
@@ -4174,124 +4174,120 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>237</v>
-      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>239</v>
+        <v>94</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>244</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
@@ -4304,111 +4300,113 @@
         <v>44</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>249</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>209</v>
+        <v>56</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J69" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>257</v>
+        <v>172</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>57</v>
@@ -4424,18 +4422,18 @@
         <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>90</v>
+        <v>259</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>56</v>
@@ -4448,27 +4446,27 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>57</v>
@@ -4478,57 +4476,57 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>63</v>
+        <v>266</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>265</v>
+        <v>202</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>269</v>
+        <v>71</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>57</v>
@@ -4538,24 +4536,24 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>271</v>
+        <v>94</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>56</v>
@@ -4571,21 +4569,21 @@
         <v>273</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="C76" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
@@ -4598,27 +4596,27 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>38</v>
@@ -4628,18 +4626,18 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J77" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>280</v>
@@ -4648,7 +4646,7 @@
         <v>281</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>57</v>
@@ -4664,48 +4662,48 @@
         <v>44</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>63</v>
+        <v>283</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
@@ -4718,24 +4716,24 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>53</v>
+        <v>286</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>169</v>
+        <v>290</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>56</v>
@@ -4748,40 +4746,40 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J82" s="3">
         <v>0</v>
@@ -4789,72 +4787,70 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>90</v>
+        <v>295</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J83" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>295</v>
+        <v>63</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>297</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J84" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>71</v>
@@ -4870,24 +4866,24 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>56</v>
@@ -4900,87 +4896,89 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>168</v>
+        <v>307</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F88" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>57</v>
@@ -4990,27 +4988,27 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J89" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>314</v>
+        <v>183</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>57</v>
@@ -5020,24 +5018,24 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>56</v>
@@ -5050,27 +5048,27 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J91" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>57</v>
@@ -5080,27 +5078,27 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>196</v>
+        <v>325</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>57</v>
@@ -5110,70 +5108,70 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>90</v>
+        <v>327</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J94" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>180</v>
+        <v>71</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J95" s="3">
         <v>0</v>
@@ -5181,133 +5179,133 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>329</v>
+        <v>94</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>332</v>
+        <v>63</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>336</v>
+        <v>183</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J98" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>175</v>
+        <v>340</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>169</v>
+        <v>341</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J99" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>56</v>
@@ -5320,57 +5318,57 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J100" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>344</v>
+        <v>182</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>209</v>
+        <v>56</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J101" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>336</v>
+        <v>173</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>37</v>
+        <v>174</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>57</v>
@@ -5380,27 +5378,27 @@
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>57</v>
@@ -5410,27 +5408,27 @@
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J103" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>196</v>
+        <v>354</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>56</v>
+        <v>237</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>57</v>
@@ -5440,27 +5438,27 @@
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J104" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>57</v>
@@ -5470,27 +5468,27 @@
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J105" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>57</v>
@@ -5500,27 +5498,27 @@
         <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J106" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>180</v>
+        <v>341</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>38</v>
@@ -5530,117 +5528,117 @@
         <v>22</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J107" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>268</v>
+        <v>365</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>262</v>
+        <v>366</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J108" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="J109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>175</v>
+        <v>368</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>169</v>
+        <v>369</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>56</v>
+        <v>237</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J110" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>57</v>
@@ -5650,57 +5648,57 @@
         <v>22</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J111" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>372</v>
+        <v>213</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J112" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>377</v>
+        <v>264</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>57</v>
@@ -5710,87 +5708,87 @@
         <v>22</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J113" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>380</v>
+        <v>267</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J114" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>343</v>
+        <v>383</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>262</v>
+        <v>71</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J115" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>38</v>
@@ -5800,24 +5798,24 @@
         <v>22</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J116" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>56</v>
@@ -5830,81 +5828,83 @@
         <v>22</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J117" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>63</v>
+        <v>389</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J118" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>60</v>
+        <v>392</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>169</v>
+        <v>394</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>56</v>
+        <v>394</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F119" s="3"/>
+      <c r="F119" s="3" t="s">
+        <v>395</v>
+      </c>
       <c r="G119" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J119" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>394</v>
@@ -5913,154 +5913,122 @@
         <v>394</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="J120" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>394</v>
+        <v>137</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="J121" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>133</v>
+        <v>394</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J122" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>394</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J123" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="I124" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J124" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J124"/>
+  <autoFilter ref="A1:J123"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6184,7 +6152,6 @@
     <hyperlink ref="H121" r:id="rId120"/>
     <hyperlink ref="H122" r:id="rId121"/>
     <hyperlink ref="H123" r:id="rId122"/>
-    <hyperlink ref="H124" r:id="rId123"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6193,7 +6160,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -6226,13 +6193,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6240,37 +6207,37 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6278,18 +6245,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6297,18 +6264,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6316,18 +6283,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6335,18 +6302,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6354,18 +6321,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6373,18 +6340,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>259</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>265</v>
+        <v>71</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6392,18 +6359,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>169</v>
+        <v>264</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6411,18 +6378,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6430,18 +6397,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6449,18 +6416,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>306</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6468,18 +6435,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6487,18 +6454,18 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6506,18 +6473,18 @@
         <v>22</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6525,18 +6492,18 @@
         <v>22</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>371</v>
+        <v>74</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6544,18 +6511,18 @@
         <v>22</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -6563,15 +6530,15 @@
         <v>22</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>386</v>
+        <v>267</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>71</v>
@@ -6582,49 +6549,11 @@
         <v>22</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G20"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6645,8 +6574,6 @@
     <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
     <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6676,7 +6603,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6695,7 +6622,7 @@
         <v>419</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -6703,12 +6630,12 @@
         <v>420</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -6716,7 +6643,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
@@ -6793,7 +6720,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6807,7 +6734,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -6826,12 +6753,12 @@
         <v>70</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6839,7 +6766,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6847,7 +6774,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6871,7 +6798,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6879,7 +6806,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6887,7 +6814,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6895,7 +6822,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>268</v>
+        <v>182</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6903,7 +6830,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>286</v>
+        <v>201</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6911,7 +6838,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>288</v>
+        <v>213</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6919,10 +6846,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>111</v>
+        <v>267</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6933,7 +6860,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
@@ -6957,13 +6884,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3">
-        <v>21.6</v>
+        <v>25.9</v>
       </c>
       <c r="D2" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -6971,13 +6898,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -6999,7 +6926,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3">
         <v>14.0</v>
@@ -7013,7 +6940,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3">
         <v>11.3</v>
@@ -7027,7 +6954,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C7" s="3">
         <v>7.2</v>
@@ -7069,7 +6996,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3">
         <v>5.8</v>
@@ -7083,10 +7010,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C11" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -7097,7 +7024,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C12" s="3">
         <v>2.9</v>
@@ -7111,7 +7038,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -7125,7 +7052,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>268</v>
+        <v>201</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -7139,7 +7066,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>288</v>
+        <v>213</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -7153,13 +7080,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7201,7 +7128,7 @@
         <v>57</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>436</v>
@@ -7212,7 +7139,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>437</v>
@@ -7242,15 +7169,15 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -7258,20 +7185,20 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -7279,7 +7206,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>394</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3">
         <v>4</v>
@@ -7287,15 +7214,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>394</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -7303,7 +7230,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -7368,10 +7295,10 @@
         <v>441</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>442</v>
@@ -7403,7 +7330,7 @@
         <v>446</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>447</v>
@@ -7429,28 +7356,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F4" s="3">
         <v>71</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="F4" s="3">
-        <v>100</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>44</v>
@@ -7461,28 +7388,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="F5" s="3">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>44</v>
@@ -7493,28 +7420,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>169</v>
+        <v>375</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -7525,28 +7452,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>373</v>
+        <v>214</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>44</v>
@@ -7557,25 +7484,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>468</v>
+        <v>152</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="F8" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>469</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>470</v>
@@ -7592,10 +7519,10 @@
         <v>471</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
+        <v>472</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>442</v>
@@ -7604,13 +7531,13 @@
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -7621,13 +7548,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>196</v>
+        <v>477</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>442</v>
@@ -7636,13 +7563,13 @@
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7653,25 +7580,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>479</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>480</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>481</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>482</v>
@@ -7688,10 +7615,10 @@
         <v>483</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>287</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>442</v>
@@ -7703,7 +7630,7 @@
         <v>484</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>485</v>
@@ -7720,25 +7647,25 @@
         <v>486</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>275</v>
+        <v>487</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7749,13 +7676,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>490</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>442</v>
@@ -7781,28 +7708,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7813,28 +7740,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="F16" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7845,28 +7772,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F17" s="3">
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7877,28 +7804,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7909,28 +7836,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>44</v>
@@ -7941,25 +7868,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>512</v>
+        <v>450</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>514</v>
+        <v>202</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>442</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>515</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>516</v>
@@ -7979,22 +7906,22 @@
         <v>518</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>464</v>
+        <v>519</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-19T05:39:50</t>
+    <t xml:space="preserve">2026-05-19T10:01:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -303,108 +303,105 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
+    <t xml:space="preserve">Director of AI Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post Sale DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7821578&amp;gh_jid=7821578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of AI Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Sale DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Torq</t>
   </si>
   <si>
@@ -537,15 +534,21 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
     <t xml:space="preserve">Glassbox</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
   </si>
   <si>
@@ -555,12 +558,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4414226464</t>
   </si>
   <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
     <t xml:space="preserve">Upstream Security</t>
   </si>
   <si>
@@ -576,19 +573,43 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4408746535</t>
   </si>
   <si>
+    <t xml:space="preserve">Discreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+  </si>
+  <si>
     <t xml:space="preserve">Deepdub</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
   </si>
   <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+    <t xml:space="preserve">DevOps Engineer 234407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-234407-at-experis-israel-4412205944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
   </si>
   <si>
     <t xml:space="preserve">eko</t>
@@ -606,7 +627,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-17</t>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cycode-4413964734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer - Sub contractor (for 7 months)</t>
@@ -621,69 +672,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-for-7-months-at-samsung-semiconductor-4416091431</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 234407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-234407-at-experis-israel-4412205944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (100656)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-100656-at-elad-software-systems-4416239061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cycode-4413964734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autodesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
-  </si>
-  <si>
     <t xml:space="preserve">Play Perfect</t>
   </si>
   <si>
@@ -699,6 +687,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
   </si>
   <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
     <t xml:space="preserve">SailPoint</t>
   </si>
   <si>
@@ -714,6 +711,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4408668742</t>
   </si>
   <si>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
   </si>
   <si>
@@ -726,18 +735,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Team Leader, Israel</t>
   </si>
   <si>
@@ -777,13 +774,196 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
   </si>
   <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Full Stack &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seegnal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-full-stack-devops-engineer-at-seegnal-4412217630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placer.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-placer-ai-4375474671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-platform-at-toluna-4400400595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
   </si>
   <si>
     <t xml:space="preserve">Zenity</t>
@@ -792,391 +972,175 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
   </si>
   <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LayerX Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-kela-technologies-4410027133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playermaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Manager</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-allpha-innovation-4413893764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4415415831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placer.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-placer-ai-4375474671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellular DevOps SW Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cellular-devops-sw-engineer-at-apple-4414170146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4410353746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LayerX Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-kela-technologies-4410027133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playermaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22490 - System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
@@ -1329,10 +1293,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9%</t>
+    <t xml:space="preserve">59.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1371,198 +1335,180 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4416210373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control-M System Administrator 3047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isracard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/control-m-system-administrator-3047-at-isracard-4405630305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier II III UC Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTEC Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyderabad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-tier-ii-iii-uc-support-engineer-ttec-digital-1131561</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36330)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36330-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4414582227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control-M System Administrator 3047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isracard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/control-m-system-administrator-3047-at-isracard-4405630305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier II III UC Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTEC Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-tier-ii-iii-uc-support-engineer-ttec-digital-1131561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4414971429</t>
-  </si>
-  <si>
     <t xml:space="preserve">Eitan Medical</t>
   </si>
   <si>
@@ -1587,6 +1533,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1614,7 +1566,7 @@
     <t xml:space="preserve">Git</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform/IaC</t>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1766,7 +1718,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -1774,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1782,7 +1734,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1790,7 +1742,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -1862,7 +1814,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -1870,7 +1822,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -1897,12 +1849,12 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B2" s="3">
         <v>18</v>
@@ -1910,7 +1862,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="B3" s="3">
         <v>9</v>
@@ -1918,7 +1870,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1926,7 +1878,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1934,7 +1886,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1953,47 +1905,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -2001,7 +1953,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -2009,7 +1961,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -2017,7 +1969,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="B9" s="3">
         <v>10</v>
@@ -2025,7 +1977,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -2033,31 +1985,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>418</v>
+        <v>513</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>529</v>
+        <v>406</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="B14" s="3">
         <v>4</v>
@@ -2065,7 +2017,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -2073,10 +2025,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2101,13 +2053,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2">
@@ -2115,13 +2067,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>15.4</v>
+        <v>14.6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2130,19 +2082,19 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3">
-        <v>38.6</v>
+        <v>34.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -2151,7 +2103,7 @@
         <v>1.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2163,70 +2115,70 @@
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>84.2</v>
+        <v>33.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>22.9</v>
+        <v>19.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2831,7 +2783,7 @@
         <v>87</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>56</v>
@@ -2840,13 +2792,13 @@
         <v>57</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>41</v>
@@ -2857,13 +2809,13 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>56</v>
@@ -2889,7 +2841,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>87</v>
@@ -2901,16 +2853,16 @@
         <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>41</v>
@@ -2921,13 +2873,13 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>56</v>
@@ -2936,27 +2888,27 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>56</v>
@@ -2977,18 +2929,18 @@
         <v>111</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>56</v>
@@ -2997,126 +2949,126 @@
         <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="J24" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="J26" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>56</v>
@@ -3127,14 +3079,12 @@
       <c r="E28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
@@ -3145,26 +3095,28 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
@@ -3175,28 +3127,28 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
@@ -3207,10 +3159,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>56</v>
@@ -3219,16 +3171,16 @@
         <v>56</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
@@ -3239,28 +3191,28 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
@@ -3271,10 +3223,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>55</v>
@@ -3286,13 +3238,13 @@
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
@@ -3303,28 +3255,28 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>41</v>
@@ -3335,13 +3287,13 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>56</v>
@@ -3350,13 +3302,13 @@
         <v>57</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>41</v>
@@ -3367,28 +3319,28 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D36" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>41</v>
@@ -3399,13 +3351,13 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>56</v>
@@ -3414,13 +3366,13 @@
         <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>41</v>
@@ -3431,48 +3383,46 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>163</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>57</v>
@@ -3482,7 +3432,7 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>44</v>
@@ -3493,46 +3443,46 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>57</v>
@@ -3542,7 +3492,7 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>80</v>
@@ -3553,10 +3503,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>71</v>
@@ -3572,7 +3522,7 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>44</v>
@@ -3583,16 +3533,16 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>71</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>57</v>
@@ -3602,24 +3552,24 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>71</v>
+        <v>182</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>56</v>
@@ -3632,27 +3582,27 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>57</v>
@@ -3662,37 +3612,37 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>44</v>
@@ -3703,26 +3653,26 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>44</v>
@@ -3733,13 +3683,13 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>56</v>
@@ -3752,24 +3702,24 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
@@ -3782,24 +3732,24 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
@@ -3812,27 +3762,27 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>203</v>
+        <v>136</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>57</v>
@@ -3859,40 +3809,40 @@
         <v>206</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="D53" s="3" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>57</v>
@@ -3902,7 +3852,7 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>80</v>
@@ -3913,16 +3863,16 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>57</v>
@@ -3932,30 +3882,30 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3965,51 +3915,51 @@
         <v>218</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="J56" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
@@ -4022,54 +3972,54 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
@@ -4082,27 +4032,27 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>57</v>
@@ -4112,42 +4062,42 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J61" s="3">
         <v>1</v>
@@ -4155,16 +4105,16 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>94</v>
+        <v>238</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>57</v>
@@ -4174,27 +4124,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="J62" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>239</v>
+        <v>126</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>57</v>
@@ -4204,54 +4154,54 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>94</v>
+        <v>243</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>56</v>
@@ -4264,7 +4214,7 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>44</v>
@@ -4275,26 +4225,28 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>249</v>
+      </c>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>44</v>
@@ -4305,64 +4257,62 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>250</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>183</v>
+        <v>256</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4370,10 +4320,10 @@
         <v>63</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>56</v>
@@ -4386,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>44</v>
@@ -4397,76 +4347,76 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>172</v>
+        <v>260</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J70" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>57</v>
@@ -4476,27 +4426,27 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>203</v>
+        <v>56</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>57</v>
@@ -4506,24 +4456,24 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>56</v>
@@ -4536,7 +4486,7 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>44</v>
@@ -4547,13 +4497,13 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>94</v>
+        <v>272</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>183</v>
+        <v>256</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>56</v>
@@ -4566,87 +4516,87 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>94</v>
+        <v>277</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>63</v>
+        <v>280</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>277</v>
+        <v>71</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>281</v>
+        <v>182</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>57</v>
@@ -4656,24 +4606,24 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J78" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
@@ -4686,24 +4636,24 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
@@ -4711,12 +4661,14 @@
       <c r="E80" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>44</v>
@@ -4727,13 +4679,13 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>56</v>
@@ -4746,7 +4698,7 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>44</v>
@@ -4757,43 +4709,43 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>56</v>
@@ -4806,24 +4758,24 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>56</v>
@@ -4836,57 +4788,57 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J84" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>71</v>
+        <v>305</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>56</v>
+        <v>211</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>57</v>
@@ -4896,27 +4848,27 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>188</v>
+        <v>311</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>57</v>
@@ -4926,7 +4878,7 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>80</v>
@@ -4937,13 +4889,13 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>309</v>
+        <v>126</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>56</v>
@@ -4951,44 +4903,42 @@
       <c r="E88" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>311</v>
-      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J88" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>71</v>
+        <v>182</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>44</v>
@@ -4999,16 +4949,16 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>56</v>
+        <v>211</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>57</v>
@@ -5018,87 +4968,87 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>318</v>
+        <v>126</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="J91" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>228</v>
+        <v>322</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>203</v>
+        <v>56</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J92" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>57</v>
@@ -5108,7 +5058,7 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>44</v>
@@ -5119,13 +5069,13 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>328</v>
+        <v>181</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>56</v>
@@ -5138,24 +5088,24 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>56</v>
@@ -5168,27 +5118,27 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>94</v>
+        <v>334</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>57</v>
@@ -5198,7 +5148,7 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>44</v>
@@ -5209,29 +5159,29 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>188</v>
+        <v>327</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J97" s="3">
         <v>1</v>
@@ -5239,46 +5189,46 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>183</v>
+        <v>340</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J98" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>57</v>
@@ -5288,7 +5238,7 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>44</v>
@@ -5299,76 +5249,76 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>198</v>
+        <v>327</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J100" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>182</v>
+        <v>349</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J101" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>173</v>
+        <v>353</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>57</v>
@@ -5378,27 +5328,27 @@
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J102" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>348</v>
+        <v>74</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>37</v>
+        <v>232</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>57</v>
@@ -5408,27 +5358,27 @@
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="J103" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>57</v>
@@ -5438,27 +5388,27 @@
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J104" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>57</v>
@@ -5468,100 +5418,100 @@
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J105" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>360</v>
+        <v>203</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>361</v>
+        <v>215</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="J106" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>366</v>
+        <v>71</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J108" s="3">
         <v>1</v>
@@ -5569,16 +5519,16 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>74</v>
+        <v>371</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>369</v>
+        <v>172</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>57</v>
@@ -5588,7 +5538,7 @@
         <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>80</v>
@@ -5599,49 +5549,49 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>371</v>
+        <v>63</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>368</v>
+        <v>209</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J110" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>373</v>
+        <v>322</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>375</v>
+        <v>188</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
@@ -5651,10 +5601,10 @@
         <v>376</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J111" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -5662,23 +5612,23 @@
         <v>377</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>213</v>
+        <v>378</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>44</v>
@@ -5689,116 +5639,124 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>264</v>
+        <v>382</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>137</v>
+        <v>382</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F113" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="G113" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J113" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>267</v>
+        <v>386</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>71</v>
+        <v>382</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>56</v>
+        <v>382</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F114" s="3"/>
+      <c r="F114" s="3" t="s">
+        <v>387</v>
+      </c>
       <c r="G114" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="J114" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>71</v>
+        <v>391</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F115" s="3"/>
+      <c r="F115" s="3" t="s">
+        <v>392</v>
+      </c>
       <c r="G115" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="J115" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>63</v>
+        <v>394</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>201</v>
+        <v>395</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>202</v>
+        <v>396</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>203</v>
+        <v>382</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F116" s="3"/>
+      <c r="F116" s="3" t="s">
+        <v>397</v>
+      </c>
       <c r="G116" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>44</v>
@@ -5809,226 +5767,38 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>188</v>
+        <v>382</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>56</v>
+        <v>382</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>401</v>
+      </c>
       <c r="G117" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J117" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J118" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J119" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J120" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J121" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J122" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="I123" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J123" s="3">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J123"/>
+  <autoFilter ref="A1:J117"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6146,12 +5916,6 @@
     <hyperlink ref="H115" r:id="rId114"/>
     <hyperlink ref="H116" r:id="rId115"/>
     <hyperlink ref="H117" r:id="rId116"/>
-    <hyperlink ref="H118" r:id="rId117"/>
-    <hyperlink ref="H119" r:id="rId118"/>
-    <hyperlink ref="H120" r:id="rId119"/>
-    <hyperlink ref="H121" r:id="rId120"/>
-    <hyperlink ref="H122" r:id="rId121"/>
-    <hyperlink ref="H123" r:id="rId122"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6212,13 +5976,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6226,18 +5990,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6245,18 +6009,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6264,18 +6028,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6283,18 +6047,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6302,18 +6066,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6321,18 +6085,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6340,18 +6104,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>71</v>
+        <v>182</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6359,18 +6123,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6378,18 +6142,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6397,18 +6161,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6416,18 +6180,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>306</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6435,18 +6199,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>183</v>
+        <v>311</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6454,18 +6218,18 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>301</v>
+        <v>346</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6473,18 +6237,18 @@
         <v>22</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>341</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6492,7 +6256,7 @@
         <v>22</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18">
@@ -6500,10 +6264,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6511,18 +6275,18 @@
         <v>22</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -6530,18 +6294,18 @@
         <v>22</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>267</v>
+        <v>372</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -6549,7 +6313,7 @@
         <v>22</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -6587,23 +6351,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6611,31 +6375,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>420</v>
+        <v>291</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>311</v>
+        <v>408</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -6643,23 +6407,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -6667,7 +6431,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B11" s="3">
         <v>14</v>
@@ -6675,23 +6439,23 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -6699,7 +6463,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -6707,7 +6471,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -6720,7 +6484,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6729,7 +6493,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
@@ -6737,7 +6501,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -6758,7 +6522,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6766,7 +6530,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6774,15 +6538,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>301</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6790,7 +6554,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6798,7 +6562,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6806,7 +6570,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6814,7 +6578,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6822,7 +6586,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6830,7 +6594,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>201</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6838,7 +6602,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6846,10 +6610,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6867,16 +6631,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
@@ -6901,10 +6665,10 @@
         <v>87</v>
       </c>
       <c r="C3" s="3">
-        <v>21.6</v>
+        <v>18.5</v>
       </c>
       <c r="D3" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -6926,7 +6690,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="3">
         <v>14.0</v>
@@ -6940,7 +6704,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C6" s="3">
         <v>11.3</v>
@@ -6954,7 +6718,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="3">
         <v>7.2</v>
@@ -6996,7 +6760,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" s="3">
         <v>5.8</v>
@@ -7010,13 +6774,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>301</v>
+        <v>127</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -7024,13 +6788,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -7038,7 +6802,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -7052,7 +6816,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -7066,13 +6830,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>213</v>
+        <v>381</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -7080,10 +6844,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -7106,21 +6870,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3">
@@ -7128,10 +6892,10 @@
         <v>57</v>
       </c>
       <c r="B3" s="3">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4">
@@ -7139,10 +6903,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -7161,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
@@ -7169,15 +6933,15 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -7190,7 +6954,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -7198,15 +6962,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="B7" s="3">
         <v>4</v>
@@ -7214,7 +6978,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B8" s="3">
         <v>4</v>
@@ -7222,7 +6986,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -7230,7 +6994,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -7257,10 +7021,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7272,10 +7036,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -7292,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>87</v>
@@ -7301,19 +7065,19 @@
         <v>88</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7324,28 +7088,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>44</v>
@@ -7356,28 +7120,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F4" s="3">
+        <v>57</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="F4" s="3">
-        <v>71</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>44</v>
@@ -7388,28 +7152,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>183</v>
+        <v>362</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>44</v>
@@ -7420,31 +7184,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>375</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="F6" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -7452,31 +7216,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="F7" s="3">
         <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -7484,28 +7248,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F8" s="3">
         <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>44</v>
@@ -7516,28 +7280,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -7548,28 +7312,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7580,7 +7344,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>35</v>
@@ -7589,19 +7353,19 @@
         <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F11" s="3">
         <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7612,28 +7376,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F12" s="3">
         <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -7644,28 +7408,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F13" s="3">
         <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7676,28 +7440,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F14" s="3">
         <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7708,28 +7472,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F15" s="3">
         <v>37</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7740,28 +7504,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="F16" s="3">
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7772,28 +7536,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="F17" s="3">
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7804,28 +7568,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F18" s="3">
         <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7836,28 +7600,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>44</v>
@@ -7868,28 +7632,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>450</v>
+        <v>499</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>442</v>
+        <v>501</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -7900,28 +7664,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>519</v>
+        <v>445</v>
       </c>
       <c r="F21" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="541">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-19T10:01:46</t>
+    <t xml:space="preserve">2026-05-20T05:09:44</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -534,6 +534,18 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4415902208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">SessionCam</t>
   </si>
   <si>
@@ -546,33 +558,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
   </si>
   <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4414226464</t>
+  </si>
+  <si>
     <t xml:space="preserve">Glassbox</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
   </si>
   <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4414226464</t>
-  </si>
-  <si>
     <t xml:space="preserve">Upstream Security</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
   </si>
   <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4408746535</t>
-  </si>
-  <si>
     <t xml:space="preserve">Discreet</t>
   </si>
   <si>
@@ -597,34 +600,31 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer 234407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-234407-at-experis-israel-4412205944</t>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4414506870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFTECH-IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-17</t>
   </si>
   <si>
-    <t xml:space="preserve">eko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4414506870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFTECH-IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cycode-4413964734</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Infrastructure Specialist</t>
@@ -636,13 +636,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cycode-4413964734</t>
+    <t xml:space="preserve">DevOps Engineer - Sub contractor (for 7 months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Semiconductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-for-7-months-at-samsung-semiconductor-4416091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
@@ -660,16 +669,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer - Sub contractor (for 7 months)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-for-7-months-at-samsung-semiconductor-4416091431</t>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
   </si>
   <si>
     <t xml:space="preserve">Play Perfect</t>
@@ -678,28 +693,40 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
+    <t xml:space="preserve">SailPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
   </si>
   <si>
     <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
   </si>
   <si>
-    <t xml:space="preserve">SailPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud Engineer</t>
@@ -711,28 +738,82 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4408668742</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
+    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freightos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Team Leader, Israel</t>
@@ -741,37 +822,79 @@
     <t xml:space="preserve">AlgoSec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4416466723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freightos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4417005682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4415415831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
@@ -783,22 +906,76 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Full Stack &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seegnal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-full-stack-devops-engineer-at-seegnal-4412217630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellular DevOps SW Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cellular-devops-sw-engineer-at-apple-4414170146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
   </si>
   <si>
     <t xml:space="preserve">Akeyless Security</t>
@@ -807,130 +984,7 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placer.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-placer-ai-4375474671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer (Platform)</t>
+    <t xml:space="preserve">Cloud Engineer (Test Automation)</t>
   </si>
   <si>
     <t xml:space="preserve">Toluna</t>
@@ -939,52 +993,19 @@
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-platform-at-toluna-4400400595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-test-automation-at-toluna-4400191621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Infrastructure Engineer</t>
@@ -996,82 +1017,79 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
   </si>
   <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
+    <t xml:space="preserve">IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playermaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-coralogix-4343793999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
   </si>
   <si>
     <t xml:space="preserve">Senior System Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-kela-technologies-4410027133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playermaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
   </si>
   <si>
     <t xml:space="preserve">‫System Engineer</t>
@@ -1080,25 +1098,28 @@
     <t xml:space="preserve">JobsSeek</t>
   </si>
   <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
   </si>
   <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4413301795</t>
   </si>
   <si>
     <t xml:space="preserve">PHY System Engineer</t>
@@ -1125,6 +1146,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
   </si>
   <si>
+    <t xml:space="preserve">22490 - System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-milestone-systems-4416490430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevOps Manager</t>
   </si>
   <si>
@@ -1134,24 +1179,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
   </si>
   <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-coralogix-4343793999</t>
-  </si>
-  <si>
     <t xml:space="preserve">Software Engineering Manager - SRE</t>
   </si>
   <si>
@@ -1293,10 +1332,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">59.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5%</t>
+    <t xml:space="preserve">62.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1308,31 +1347,46 @@
     <t xml:space="preserve">Stack</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
     <t xml:space="preserve">Developer Support Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">JFrog</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-jfrog-4410725405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
@@ -1434,18 +1488,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
     <t xml:space="preserve">Port.io</t>
   </si>
   <si>
@@ -1467,6 +1509,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
   </si>
   <si>
+    <t xml:space="preserve">Regulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
+  </si>
+  <si>
     <t xml:space="preserve">Control-M System Administrator 3047</t>
   </si>
   <si>
@@ -1491,6 +1545,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier II III UC Support Engineer</t>
   </si>
   <si>
@@ -1506,67 +1572,49 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-tier-ii-iii-uc-support-engineer-ttec-digital-1131561</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
     <t xml:space="preserve">Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1718,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -1726,7 +1774,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1734,7 +1782,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -1742,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -1814,7 +1862,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -1849,28 +1897,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1878,7 +1926,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1886,7 +1934,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>440</v>
+        <v>521</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1905,55 +1953,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B4" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>509</v>
+        <v>234</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>236</v>
+        <v>422</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -1961,63 +2009,63 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>409</v>
+        <v>525</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>513</v>
+        <v>419</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>406</v>
+        <v>529</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>515</v>
+        <v>421</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -2025,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>405</v>
+        <v>531</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2053,13 +2101,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2">
@@ -2070,10 +2118,10 @@
         <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2082,28 +2130,28 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3">
-        <v>34.9</v>
+        <v>33.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2118,67 +2166,67 @@
         <v>0.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.2</v>
+        <v>36.4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.0</v>
+        <v>20.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>6.9</v>
+        <v>8.8</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2190,7 +2238,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2262,7 +2310,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2294,7 +2342,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2326,7 +2374,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2356,7 +2404,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2388,7 +2436,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2420,7 +2468,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2452,7 +2500,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2484,7 +2532,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2516,7 +2564,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2548,7 +2596,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2580,7 +2628,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -2612,7 +2660,7 @@
         <v>80</v>
       </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2644,7 +2692,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -2676,7 +2724,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2708,7 +2756,7 @@
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2740,7 +2788,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -2772,7 +2820,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2804,7 +2852,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2836,7 +2884,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -2868,7 +2916,7 @@
         <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2900,7 +2948,7 @@
         <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2932,7 +2980,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -2964,7 +3012,7 @@
         <v>116</v>
       </c>
       <c r="J24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2996,7 +3044,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -3028,7 +3076,7 @@
         <v>116</v>
       </c>
       <c r="J26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3060,7 +3108,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -3090,7 +3138,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -3122,7 +3170,7 @@
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -3154,7 +3202,7 @@
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -3186,7 +3234,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -3218,7 +3266,7 @@
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -3250,7 +3298,7 @@
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -3282,7 +3330,7 @@
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -3314,7 +3362,7 @@
         <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -3346,7 +3394,7 @@
         <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -3378,7 +3426,7 @@
         <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -3408,7 +3456,7 @@
         <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -3438,7 +3486,7 @@
         <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -3452,7 +3500,7 @@
         <v>172</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>57</v>
@@ -3462,10 +3510,10 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="J40" s="3">
         <v>0</v>
@@ -3479,10 +3527,10 @@
         <v>175</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>57</v>
@@ -3492,13 +3540,13 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3506,7 +3554,7 @@
         <v>126</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>71</v>
@@ -3522,13 +3570,13 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J42" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3536,13 +3584,13 @@
         <v>126</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>57</v>
@@ -3552,10 +3600,10 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J43" s="3">
         <v>1</v>
@@ -3566,10 +3614,10 @@
         <v>126</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>56</v>
@@ -3582,13 +3630,13 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -3596,10 +3644,10 @@
         <v>126</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>136</v>
@@ -3612,13 +3660,13 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3626,10 +3674,10 @@
         <v>126</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>56</v>
@@ -3642,13 +3690,13 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J46" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3656,10 +3704,10 @@
         <v>63</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>56</v>
@@ -3672,24 +3720,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>56</v>
@@ -3702,24 +3750,24 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
@@ -3732,13 +3780,13 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3749,13 +3797,13 @@
         <v>200</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
@@ -3765,10 +3813,10 @@
         <v>201</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3779,7 +3827,7 @@
         <v>203</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>136</v>
@@ -3798,7 +3846,7 @@
         <v>80</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3809,40 +3857,40 @@
         <v>206</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>209</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>57</v>
@@ -3852,10 +3900,10 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="J53" s="3">
         <v>0</v>
@@ -3863,16 +3911,16 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>57</v>
@@ -3882,10 +3930,10 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J54" s="3">
         <v>1</v>
@@ -3893,13 +3941,13 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
@@ -3915,10 +3963,10 @@
         <v>218</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3929,7 +3977,7 @@
         <v>220</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
@@ -3945,21 +3993,21 @@
         <v>221</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
@@ -3972,13 +4020,13 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3986,10 +4034,10 @@
         <v>126</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>56</v>
@@ -4002,24 +4050,24 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
@@ -4032,13 +4080,13 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -4046,13 +4094,13 @@
         <v>126</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>57</v>
@@ -4062,24 +4110,24 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>136</v>
@@ -4088,33 +4136,33 @@
         <v>57</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>57</v>
@@ -4124,81 +4172,81 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>126</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>44</v>
+        <v>198</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>71</v>
@@ -4214,13 +4262,13 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -4228,10 +4276,10 @@
         <v>150</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>136</v>
@@ -4240,60 +4288,60 @@
         <v>57</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J66" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>254</v>
+        <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>56</v>
@@ -4306,10 +4354,10 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="J68" s="3">
         <v>0</v>
@@ -4317,32 +4365,32 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>63</v>
+        <v>249</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4350,10 +4398,10 @@
         <v>63</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>56</v>
@@ -4366,57 +4414,57 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>262</v>
+        <v>126</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>57</v>
@@ -4426,24 +4474,24 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J72" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>56</v>
@@ -4456,27 +4504,27 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>57</v>
@@ -4486,27 +4534,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>57</v>
@@ -4516,27 +4564,27 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>277</v>
+        <v>63</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
@@ -4546,21 +4594,21 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>71</v>
@@ -4571,32 +4619,34 @@
       <c r="E77" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>182</v>
+        <v>281</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>57</v>
@@ -4606,24 +4656,24 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
@@ -4636,24 +4686,24 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
@@ -4661,31 +4711,29 @@
       <c r="E80" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>291</v>
-      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>56</v>
@@ -4698,54 +4746,54 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>56</v>
@@ -4758,70 +4806,70 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>67</v>
+        <v>298</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>305</v>
+        <v>172</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>232</v>
+        <v>56</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="J85" s="3">
         <v>2</v>
@@ -4829,16 +4877,16 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>227</v>
+        <v>304</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>57</v>
@@ -4848,27 +4896,27 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>311</v>
+        <v>172</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>57</v>
@@ -4878,100 +4926,100 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>126</v>
+        <v>309</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>63</v>
+        <v>312</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J89" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J90" s="3">
         <v>1</v>
@@ -4982,10 +5030,10 @@
         <v>126</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>56</v>
@@ -4998,10 +5046,10 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="J91" s="3">
         <v>2</v>
@@ -5009,13 +5057,13 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>56</v>
@@ -5028,27 +5076,27 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>37</v>
+        <v>230</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>57</v>
@@ -5058,87 +5106,87 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>181</v>
+        <v>326</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>182</v>
+        <v>327</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J94" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J95" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>57</v>
@@ -5148,27 +5196,27 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J96" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>327</v>
+        <v>176</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>57</v>
@@ -5178,27 +5226,27 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>340</v>
-      </c>
       <c r="D98" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>57</v>
@@ -5208,24 +5256,24 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J98" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>136</v>
@@ -5238,21 +5286,21 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J99" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>327</v>
@@ -5261,61 +5309,61 @@
         <v>37</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>136</v>
@@ -5328,57 +5376,57 @@
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="J102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>74</v>
+        <v>351</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="J103" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>355</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>356</v>
+        <v>281</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>57</v>
@@ -5388,24 +5436,24 @@
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J104" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>136</v>
@@ -5418,54 +5466,54 @@
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J105" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>215</v>
+        <v>361</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J106" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>136</v>
@@ -5478,30 +5526,30 @@
         <v>22</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J107" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="D108" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
@@ -5514,7 +5562,7 @@
         <v>116</v>
       </c>
       <c r="J108" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -5522,46 +5570,46 @@
         <v>371</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>372</v>
+        <v>203</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J109" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>63</v>
+        <v>335</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>209</v>
+        <v>373</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>211</v>
+        <v>136</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
@@ -5574,24 +5622,24 @@
         <v>44</v>
       </c>
       <c r="J110" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>322</v>
+        <v>375</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>375</v>
+        <v>260</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
@@ -5601,10 +5649,10 @@
         <v>376</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J111" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -5615,10 +5663,10 @@
         <v>378</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>215</v>
+        <v>379</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>57</v>
@@ -5628,74 +5676,70 @@
         <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J112" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>381</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>382</v>
+        <v>172</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>382</v>
+        <v>56</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F113" s="3" t="s">
-        <v>383</v>
-      </c>
+      <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="J113" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H114" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="I114" s="3" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="J114" s="3">
         <v>2</v>
@@ -5703,102 +5747,256 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>391</v>
+        <v>172</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>392</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J115" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>394</v>
+        <v>63</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>395</v>
+        <v>212</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>396</v>
+        <v>213</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>382</v>
+        <v>214</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F116" s="3" t="s">
-        <v>397</v>
-      </c>
+      <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J116" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>382</v>
+        <v>207</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>382</v>
+        <v>56</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J117" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="I119" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J119" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G120" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H117" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="I117" s="3" t="s">
+      <c r="H120" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J120" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J121" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I122" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J117" s="3">
-        <v>7</v>
+      <c r="J122" s="3">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J117"/>
+  <autoFilter ref="A1:J122"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5916,6 +6114,11 @@
     <hyperlink ref="H115" r:id="rId114"/>
     <hyperlink ref="H116" r:id="rId115"/>
     <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5923,9 +6126,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5957,21 +6160,21 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
@@ -5979,7 +6182,7 @@
         <v>126</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>172</v>
@@ -5990,18 +6193,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6009,18 +6212,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6028,18 +6231,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6047,18 +6250,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>210</v>
+        <v>323</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6066,18 +6269,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>212</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>335</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>228</v>
+        <v>348</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>215</v>
+        <v>349</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6085,18 +6288,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>229</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>238</v>
+        <v>335</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>239</v>
+        <v>360</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>361</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6104,18 +6307,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>240</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>251</v>
+        <v>363</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>252</v>
+        <v>364</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>182</v>
+        <v>365</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6123,18 +6326,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>253</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>254</v>
+        <v>377</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>255</v>
+        <v>378</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>256</v>
+        <v>379</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6142,18 +6345,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>257</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>277</v>
+        <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>278</v>
+        <v>381</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6161,18 +6364,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>279</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>286</v>
+        <v>386</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>287</v>
+        <v>387</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6180,144 +6383,11 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6331,13 +6401,6 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6351,15 +6414,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B2" s="3">
         <v>27</v>
@@ -6367,7 +6430,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6375,7 +6438,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="B4" s="3">
         <v>25</v>
@@ -6383,7 +6446,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
@@ -6391,7 +6454,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B6" s="3">
         <v>20</v>
@@ -6399,7 +6462,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -6407,7 +6470,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B8" s="3">
         <v>18</v>
@@ -6415,7 +6478,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
@@ -6423,7 +6486,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -6431,7 +6494,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B11" s="3">
         <v>14</v>
@@ -6439,7 +6502,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
@@ -6447,7 +6510,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6455,7 +6518,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -6463,7 +6526,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -6471,7 +6534,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -6484,7 +6547,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6493,7 +6556,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2">
@@ -6538,15 +6601,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>299</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6554,7 +6617,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6562,7 +6625,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6570,7 +6633,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6578,7 +6641,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6586,7 +6649,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6594,7 +6657,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6602,7 +6665,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>355</v>
+        <v>212</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6610,10 +6673,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>260</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6624,23 +6687,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2">
@@ -6774,13 +6837,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>127</v>
+        <v>299</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6788,13 +6851,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6816,7 +6879,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6830,7 +6893,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C15" s="3">
         <v>2.6</v>
@@ -6844,7 +6907,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6870,21 +6933,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3">
@@ -6892,10 +6955,10 @@
         <v>57</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4">
@@ -6903,10 +6966,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -6925,7 +6988,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
@@ -6933,7 +6996,7 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -6941,7 +7004,7 @@
         <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -6949,12 +7012,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -6962,26 +7025,26 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>232</v>
+        <v>395</v>
       </c>
       <c r="B6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>382</v>
+        <v>230</v>
       </c>
       <c r="B8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7021,10 +7084,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7036,10 +7099,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -7056,28 +7119,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>87</v>
+        <v>443</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7088,31 +7151,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -7120,28 +7183,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="F4" s="3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>44</v>
@@ -7152,28 +7215,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>362</v>
+        <v>172</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="F5" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>44</v>
@@ -7184,31 +7247,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>77</v>
+        <v>461</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>462</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>71</v>
+        <v>369</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="F6" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -7216,28 +7279,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>449</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="F7" s="3">
         <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>452</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>80</v>
@@ -7248,31 +7311,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>468</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -7280,28 +7343,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>457</v>
+        <v>151</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -7312,28 +7375,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>462</v>
+        <v>207</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7344,28 +7407,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>479</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>480</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7376,28 +7439,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F12" s="3">
         <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -7408,28 +7471,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>472</v>
+        <v>287</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7440,28 +7503,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F14" s="3">
         <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7472,28 +7535,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F15" s="3">
         <v>37</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7504,31 +7567,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>185</v>
+        <v>497</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -7536,28 +7599,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="F17" s="3">
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7568,28 +7631,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>492</v>
+        <v>172</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="F18" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7600,31 +7663,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>210</v>
+        <v>323</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -7632,28 +7695,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>185</v>
+        <v>514</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>501</v>
+        <v>449</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -7664,31 +7727,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-20T05:09:44</t>
+    <t xml:space="preserve">2026-05-20T09:51:16</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -594,10 +594,28 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
   </si>
   <si>
-    <t xml:space="preserve">Deepdub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4413396534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
   </si>
   <si>
     <t xml:space="preserve">eko</t>
@@ -654,6 +672,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
   </si>
   <si>
@@ -669,15 +696,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior DevOps</t>
   </si>
   <si>
@@ -711,12 +729,18 @@
     <t xml:space="preserve">Hadera, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4417005682</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
   </si>
   <si>
@@ -738,6 +762,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4408668742</t>
   </si>
   <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
   </si>
   <si>
@@ -747,18 +783,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
   </si>
   <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freightos</t>
   </si>
   <si>
@@ -771,19 +795,25 @@
     <t xml:space="preserve">DevOps Manager</t>
   </si>
   <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
   </si>
   <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
   </si>
   <si>
     <t xml:space="preserve">Zenity</t>
@@ -816,15 +846,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4417005682</t>
-  </si>
-  <si>
     <t xml:space="preserve">Devops Infra/cloud Engineer</t>
   </si>
   <si>
@@ -837,13 +858,91 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4415415831</t>
+    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
@@ -858,79 +957,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
   </si>
   <si>
-    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
   </si>
   <si>
     <t xml:space="preserve">Embedded Platform Engineer</t>
@@ -939,15 +972,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
   </si>
   <si>
@@ -972,6 +996,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
   </si>
   <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-millennium-4372898016</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
@@ -990,9 +1020,6 @@
     <t xml:space="preserve">Toluna</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-test-automation-at-toluna-4400191621</t>
   </si>
   <si>
@@ -1053,10 +1080,118 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
   </si>
   <si>
-    <t xml:space="preserve">Playermaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4413301795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22490 - System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
   </si>
   <si>
     <t xml:space="preserve">Coralogix</t>
@@ -1065,129 +1200,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-coralogix-4343793999</t>
   </si>
   <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4413301795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22490 - System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-milestone-systems-4416490430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
   </si>
   <si>
@@ -1200,6 +1212,9 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Database Reliability Engineer</t>
   </si>
   <si>
@@ -1332,10 +1347,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2%</t>
+    <t xml:space="preserve">63.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1362,27 +1377,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JFrog</t>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-jfrog-4410725405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -1410,9 +1425,6 @@
     <t xml:space="preserve">Eurolaser Technologies Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -1455,21 +1467,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Technical Support</t>
   </si>
   <si>
@@ -1488,6 +1485,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
     <t xml:space="preserve">Port.io</t>
   </si>
   <si>
@@ -1497,6 +1506,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
   </si>
   <si>
+    <t xml:space="preserve">Regulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
+  </si>
+  <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
   </si>
   <si>
@@ -1509,18 +1530,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
   </si>
   <si>
-    <t xml:space="preserve">Regulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Control-M System Administrator 3047</t>
   </si>
   <si>
@@ -1572,9 +1581,6 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-tier-ii-iii-uc-support-engineer-ttec-digital-1131561</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
     <t xml:space="preserve">Menora Mivtachim Group</t>
   </si>
   <si>
@@ -1612,9 +1618,6 @@
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1766,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -1774,7 +1777,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1782,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -1790,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -1862,7 +1865,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -1897,28 +1900,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1926,7 +1929,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>458</v>
+        <v>523</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1934,7 +1937,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>521</v>
+        <v>463</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1953,31 +1956,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B4" s="3">
         <v>16</v>
@@ -1985,7 +1988,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B5" s="3">
         <v>16</v>
@@ -1993,23 +1996,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>422</v>
+        <v>527</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>525</v>
+        <v>427</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -2017,55 +2020,55 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -2073,7 +2076,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>531</v>
+        <v>423</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -2101,13 +2104,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2">
@@ -2118,10 +2121,10 @@
         <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>15.9</v>
+        <v>17.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2130,28 +2133,28 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3">
-        <v>33.8</v>
+        <v>38.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2163,70 +2166,70 @@
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>36.4</v>
+        <v>38.4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.3</v>
+        <v>16.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>8.8</v>
+        <v>6.6</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -3701,46 +3704,46 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>57</v>
@@ -3750,21 +3753,21 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>172</v>
@@ -3780,21 +3783,21 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>172</v>
@@ -3803,64 +3806,64 @@
         <v>56</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>57</v>
@@ -3870,24 +3873,24 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>56</v>
@@ -3900,27 +3903,27 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>57</v>
@@ -3930,24 +3933,24 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
@@ -3960,7 +3963,7 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>174</v>
@@ -3971,62 +3974,62 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>56</v>
+        <v>223</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -4034,7 +4037,7 @@
         <v>126</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>172</v>
@@ -4050,21 +4053,21 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>172</v>
@@ -4080,7 +4083,7 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>44</v>
@@ -4091,16 +4094,16 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>230</v>
+        <v>56</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>57</v>
@@ -4110,59 +4113,57 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>234</v>
-      </c>
+      <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>57</v>
@@ -4172,57 +4173,59 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>126</v>
+        <v>244</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>57</v>
@@ -4232,69 +4235,67 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>247</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>44</v>
@@ -4305,26 +4306,26 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>44</v>
@@ -4335,40 +4336,42 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>255</v>
+      </c>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>176</v>
@@ -4384,7 +4387,7 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>80</v>
@@ -4398,10 +4401,10 @@
         <v>63</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>56</v>
@@ -4414,27 +4417,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>126</v>
+        <v>257</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>57</v>
@@ -4444,87 +4447,87 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>259</v>
+        <v>60</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>262</v>
+        <v>63</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>57</v>
@@ -4534,27 +4537,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>57</v>
@@ -4567,27 +4570,27 @@
         <v>271</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>63</v>
+        <v>272</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>273</v>
+        <v>71</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
@@ -4597,10 +4600,10 @@
         <v>274</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J76" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4611,17 +4614,15 @@
         <v>276</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>71</v>
+        <v>277</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>277</v>
-      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
@@ -4629,10 +4630,10 @@
         <v>278</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J77" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4703,7 +4704,7 @@
         <v>287</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
@@ -4823,10 +4824,10 @@
         <v>299</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>71</v>
+        <v>300</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>57</v>
@@ -4836,24 +4837,24 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>56</v>
@@ -4866,24 +4867,24 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="J85" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>56</v>
@@ -4896,24 +4897,24 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J86" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>56</v>
@@ -4921,12 +4922,14 @@
       <c r="E87" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>44</v>
@@ -4937,10 +4940,10 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>172</v>
@@ -4949,14 +4952,14 @@
         <v>56</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>44</v>
@@ -4967,10 +4970,10 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>71</v>
@@ -4986,21 +4989,21 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>172</v>
@@ -5016,24 +5019,24 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>56</v>
@@ -5046,24 +5049,24 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>63</v>
+        <v>322</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>56</v>
@@ -5076,27 +5079,27 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J92" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>323</v>
+        <v>172</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>230</v>
+        <v>56</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>57</v>
@@ -5106,27 +5109,27 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>325</v>
+        <v>126</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>327</v>
+        <v>213</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>57</v>
@@ -5139,21 +5142,21 @@
         <v>328</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J94" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="C95" s="3" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>56</v>
@@ -5166,7 +5169,7 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>116</v>
@@ -5177,16 +5180,16 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>57</v>
@@ -5196,27 +5199,27 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J96" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D97" s="3" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>57</v>
@@ -5237,19 +5240,19 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>339</v>
+        <v>172</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>230</v>
+        <v>56</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
@@ -5259,24 +5262,24 @@
         <v>340</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J98" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>342</v>
+        <v>213</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>57</v>
@@ -5297,16 +5300,16 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>327</v>
+        <v>176</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>57</v>
@@ -5316,37 +5319,37 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="J100" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>44</v>
@@ -5357,13 +5360,13 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>136</v>
@@ -5376,27 +5379,27 @@
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>38</v>
@@ -5409,21 +5412,21 @@
         <v>354</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="J103" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>281</v>
+        <v>357</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>136</v>
@@ -5436,27 +5439,27 @@
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J104" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>57</v>
@@ -5466,24 +5469,24 @@
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J105" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>361</v>
+        <v>186</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>136</v>
@@ -5496,7 +5499,7 @@
         <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>174</v>
@@ -5507,13 +5510,13 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>365</v>
+        <v>281</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>136</v>
@@ -5529,10 +5532,10 @@
         <v>366</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -5549,7 +5552,7 @@
         <v>136</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
@@ -5559,51 +5562,51 @@
         <v>370</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="J108" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="C109" s="3" t="s">
-        <v>207</v>
+        <v>372</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J109" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>136</v>
@@ -5616,27 +5619,27 @@
         <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J110" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>260</v>
+        <v>379</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>71</v>
+        <v>380</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>57</v>
@@ -5646,81 +5649,81 @@
         <v>22</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J111" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>378</v>
+        <v>209</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>379</v>
+        <v>213</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="J112" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>60</v>
+        <v>344</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>172</v>
+        <v>277</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="J113" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>384</v>
+        <v>270</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>71</v>
@@ -5729,64 +5732,64 @@
         <v>56</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="J114" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="J115" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>212</v>
+        <v>391</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>38</v>
@@ -5796,7 +5799,7 @@
         <v>22</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>44</v>
@@ -5807,26 +5810,26 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>390</v>
+        <v>63</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>391</v>
+        <v>221</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>56</v>
+        <v>223</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>44</v>
@@ -5837,166 +5840,226 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>395</v>
+        <v>213</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>395</v>
+        <v>56</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F118" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H118" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="G118" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="I118" s="3" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="J118" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>398</v>
+        <v>63</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>399</v>
+        <v>228</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>395</v>
+        <v>172</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>395</v>
+        <v>56</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>400</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F119" s="3"/>
       <c r="G119" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="J119" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>136</v>
+        <v>400</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="J120" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="J121" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>395</v>
+        <v>136</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H122" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J122" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="I122" s="3" t="s">
+      <c r="G123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J123" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I124" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J122" s="3">
+      <c r="J124" s="3">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J122"/>
+  <autoFilter ref="A1:J124"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6119,6 +6182,8 @@
     <hyperlink ref="H120" r:id="rId119"/>
     <hyperlink ref="H121" r:id="rId120"/>
     <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6126,9 +6191,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6179,13 +6244,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6193,18 +6258,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6212,18 +6277,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6231,18 +6296,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6250,18 +6315,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>321</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>322</v>
+        <v>238</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>323</v>
+        <v>176</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6269,18 +6334,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>324</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>335</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>348</v>
+        <v>260</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>349</v>
+        <v>213</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6288,18 +6353,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>350</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>335</v>
+        <v>60</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>360</v>
+        <v>263</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>361</v>
+        <v>172</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6307,18 +6372,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>362</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>363</v>
+        <v>298</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>364</v>
+        <v>299</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>365</v>
+        <v>300</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6326,18 +6391,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>366</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>379</v>
+        <v>196</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6345,18 +6410,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>380</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>60</v>
+        <v>362</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6364,18 +6429,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>386</v>
+        <v>344</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>172</v>
+        <v>372</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6383,11 +6448,49 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>388</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6401,6 +6504,8 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6414,15 +6519,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B2" s="3">
         <v>27</v>
@@ -6430,7 +6535,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6438,7 +6543,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B4" s="3">
         <v>25</v>
@@ -6446,7 +6551,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
@@ -6454,7 +6559,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="B6" s="3">
         <v>20</v>
@@ -6462,7 +6567,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -6470,7 +6575,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B8" s="3">
         <v>18</v>
@@ -6478,7 +6583,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
@@ -6486,7 +6591,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -6494,7 +6599,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B11" s="3">
         <v>14</v>
@@ -6502,7 +6607,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
@@ -6510,7 +6615,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6518,7 +6623,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -6526,7 +6631,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -6534,7 +6639,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -6556,7 +6661,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2">
@@ -6601,7 +6706,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6649,7 +6754,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6657,7 +6762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6665,7 +6770,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6673,7 +6778,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6694,16 +6799,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2">
@@ -6837,7 +6942,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -6865,7 +6970,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6879,7 +6984,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6893,13 +6998,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>394</v>
+        <v>228</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6907,13 +7012,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>181</v>
+        <v>399</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6933,21 +7038,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3">
@@ -6955,10 +7060,10 @@
         <v>57</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4">
@@ -6969,7 +7074,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -6988,7 +7093,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2">
@@ -7025,23 +7130,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>395</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>214</v>
+        <v>400</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -7084,10 +7189,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7099,10 +7204,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -7119,28 +7224,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7151,31 +7256,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
@@ -7183,28 +7288,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F4" s="3">
         <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>44</v>
@@ -7215,28 +7320,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F5" s="3">
         <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>44</v>
@@ -7247,28 +7352,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F6" s="3">
         <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -7288,13 +7393,13 @@
         <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F7" s="3">
         <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
@@ -7311,28 +7416,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>186</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F8" s="3">
         <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>80</v>
@@ -7343,7 +7448,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>151</v>
@@ -7352,19 +7457,19 @@
         <v>152</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -7375,28 +7480,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7407,28 +7512,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>479</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>480</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7439,28 +7544,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>287</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>213</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F12" s="3">
         <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -7471,28 +7576,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>287</v>
+        <v>489</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7503,28 +7608,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F14" s="3">
         <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7535,31 +7640,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>492</v>
+        <v>456</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>172</v>
+        <v>496</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F15" s="3">
         <v>37</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -7567,31 +7672,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>452</v>
+        <v>499</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>497</v>
+        <v>172</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F16" s="3">
         <v>37</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -7599,28 +7704,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>186</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F17" s="3">
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7631,28 +7736,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F18" s="3">
         <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7663,28 +7768,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>323</v>
+        <v>196</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F19" s="3">
         <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>80</v>
@@ -7695,28 +7800,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F20" s="3">
         <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -7727,28 +7832,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>517</v>
+        <v>362</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F21" s="3">
         <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>80</v>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-20T09:51:16</t>
+    <t xml:space="preserve">2026-05-21T09:59:32</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -180,7 +180,7 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
+    <t xml:space="preserve">DevOps Tech Lead</t>
   </si>
   <si>
     <t xml:space="preserve">Unity3D</t>
@@ -192,66 +192,48 @@
     <t xml:space="preserve">Tel Aviv</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Python, Prometheus, Grafana, Pulumi, Networking, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7911982?gh_jid=7911982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Delivery Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mid</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Prometheus, Grafana, Pulumi, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7893258?gh_jid=7893258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Python, Prometheus, Grafana, Pulumi, Networking, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7911982?gh_jid=7911982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Delivery Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, CI/CD, Argo CD</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.payoneer.com/careers/position/7861540/?gh_jid=7861540</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, CI/CD, Linux, Python, Bash/Shell, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7709743/?gh_jid=7709743</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Corp System Administrator</t>
   </si>
   <si>
@@ -264,12 +246,6 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Crossplane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7548243/?gh_jid=7548243</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior DevSecOps Engineer</t>
   </si>
   <si>
@@ -312,7 +288,7 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
   </si>
   <si>
-    <t xml:space="preserve">Post Sale DevOps Engineer</t>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
@@ -546,28 +522,145 @@
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Majestic Labs ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-majestic-labs-ai-4416325504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
     <t xml:space="preserve">SessionCam</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
   </si>
   <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4414226464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
+    <t xml:space="preserve">Discreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4413396534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFTECH-IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
   </si>
   <si>
     <t xml:space="preserve">Upstream Security</t>
@@ -576,94 +669,25 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
   </si>
   <si>
-    <t xml:space="preserve">Discreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4413396534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4414506870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFTECH-IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cycode-4413964734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Sub contractor (for 7 months)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-for-7-months-at-samsung-semiconductor-4416091431</t>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
   </si>
   <si>
     <t xml:space="preserve">Silverfort</t>
@@ -672,94 +696,226 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
     <t xml:space="preserve">SailPoint</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
   </si>
   <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T&amp;S Talents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4408668742</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4417005682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4408668742</t>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
   </si>
   <si>
     <t xml:space="preserve">Cellebrite</t>
@@ -768,58 +924,220 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4416232991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior VMware &amp; VDI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-vmware-vdi-infrastructure-engineer-at-extreme-4416018203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – UAV Systems Development &amp; Integration (Aerospace)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GroWings Robotx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kadima, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-uav-systems-development-integration-aerospace-at-growings-robotx-4410552923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Frequency System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-system-engineer-at-ge-healthcare-4398024249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-milestone-systems-4416490430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-phy-system-engineer-at-nvidia-ai-4413348316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22490 - System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMware &amp; VDI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-vdi-infrastructure-engineer-at-shavit-software-4416479932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
   </si>
   <si>
     <t xml:space="preserve">Freightos</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering Manager - SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipalti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
   </si>
   <si>
     <t xml:space="preserve">Leidos</t>
@@ -828,663 +1146,366 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
   </si>
   <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
+    <t xml:space="preserve">Senior Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudlinux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform, Ansible, CI/CD, Linux, Grafana, Postgres, MongoDB, Redis, Networking, Security, Observability, OpenTofu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-senior-database-reliability-engineer-cloudlinux-1131613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevRel Content Creator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperPlane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, CI/CD, Lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-devrel-content-creator-superplane-1131594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HighLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP, Go, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-staff-engineer-platform-engineering-highlevel-1131588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kafka, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-manager-platform-engineering-natera-1131552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager AI Fleet Management &amp;amp; Honk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spotify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-engineering-manager-ai-fleet-management-amp-honk-spotify-1131520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4416210373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
     <t xml:space="preserve">Cato Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellular DevOps SW Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cellular-devops-sw-engineer-at-apple-4414170146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-millennium-4372898016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4383202046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer (Test Automation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-test-automation-at-toluna-4400191621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LayerX Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-system-engineer-at-reline-it-solutions-4413301795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22490 - System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-coralogix-4343793999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering Manager - SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipalti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudlinux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform, Ansible, CI/CD, Linux, Grafana, Postgres, MongoDB, Redis, Networking, Security, Observability, OpenTofu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-senior-database-reliability-engineer-cloudlinux-1131613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevRel Content Creator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperPlane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, CI/CD, Lambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-devrel-content-creator-superplane-1131594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HighLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Go, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-staff-engineer-platform-engineering-highlevel-1131588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafka, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-manager-platform-engineering-natera-1131552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager AI Fleet Management &amp;amp; Honk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spotify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-engineering-manager-ai-fleet-management-amp-honk-spotify-1131520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4416210373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
@@ -1506,90 +1527,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
   </si>
   <si>
-    <t xml:space="preserve">Regulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control-M System Administrator 3047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isracard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/control-m-system-administrator-3047-at-isracard-4405630305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier II III UC Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTEC Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-tier-ii-iii-uc-support-engineer-ttec-digital-1131561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -1608,16 +1545,19 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1769,7 +1709,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
@@ -1777,7 +1717,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -1785,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1793,7 +1733,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>211</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1805,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -1873,7 +1813,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
@@ -1900,28 +1840,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1929,7 +1869,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1937,7 +1877,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1956,111 +1896,111 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>524</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>432</v>
+        <v>505</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>526</v>
+        <v>410</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>242</v>
+        <v>506</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>528</v>
+        <v>196</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>424</v>
+        <v>510</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>531</v>
+        <v>401</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -2068,15 +2008,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>426</v>
+        <v>512</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -2104,13 +2044,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2">
@@ -2118,13 +2058,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
-        <v>17.8</v>
+        <v>15.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2133,28 +2073,28 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3">
-        <v>38.2</v>
+        <v>34.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2169,13 +2109,13 @@
         <v>0.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
@@ -2184,13 +2124,13 @@
         <v>38.4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -2199,37 +2139,37 @@
         <v>21.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.9</v>
+        <v>15.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2240,9 +2180,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2313,7 +2253,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2345,7 +2285,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2377,7 +2317,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2407,7 +2347,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2439,7 +2379,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2456,33 +2396,33 @@
         <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>56</v>
@@ -2503,7 +2443,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2511,7 +2451,7 @@
         <v>63</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>56</v>
@@ -2523,68 +2463,68 @@
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>72</v>
@@ -2596,283 +2536,283 @@
         <v>73</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="J11" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>102</v>
@@ -2887,82 +2827,82 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="J21" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>56</v>
@@ -2971,27 +2911,27 @@
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="J23" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>56</v>
@@ -3000,94 +2940,92 @@
         <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>56</v>
@@ -3096,30 +3034,30 @@
         <v>56</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>56</v>
@@ -3128,34 +3066,36 @@
         <v>56</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>38</v>
@@ -3173,18 +3113,18 @@
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>56</v>
@@ -3193,94 +3133,94 @@
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>56</v>
@@ -3289,444 +3229,440 @@
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>156</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J35" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>159</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J36" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>162</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="J37" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F46" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
@@ -3734,239 +3670,239 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="J51" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>56</v>
+        <v>219</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>217</v>
+        <v>53</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J55" s="3">
         <v>0</v>
@@ -3974,19 +3910,19 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>223</v>
+        <v>56</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
@@ -3996,7 +3932,7 @@
         <v>224</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="J56" s="3">
         <v>1</v>
@@ -4004,315 +3940,315 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>204</v>
+        <v>44</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J59" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>232</v>
+        <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>126</v>
+        <v>233</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D62" s="3" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F63" s="3" t="s">
+      <c r="G63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="I63" s="3" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="C64" s="3" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>126</v>
+        <v>246</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>204</v>
+        <v>44</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>56</v>
@@ -4325,72 +4261,70 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J67" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>255</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J68" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="J69" s="3">
         <v>1</v>
@@ -4398,16 +4332,16 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>63</v>
+        <v>264</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
@@ -4417,10 +4351,10 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -4428,59 +4362,59 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>181</v>
+        <v>269</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>60</v>
+        <v>271</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J72" s="3">
         <v>0</v>
@@ -4488,89 +4422,89 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>63</v>
+        <v>274</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J73" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>126</v>
+        <v>277</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>204</v>
+        <v>44</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>223</v>
+        <v>128</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="J75" s="3">
         <v>2</v>
@@ -4578,223 +4512,223 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>136</v>
+        <v>219</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>283</v>
+        <v>118</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>286</v>
+        <v>59</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J80" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>290</v>
+        <v>164</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>292</v>
+        <v>118</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>295</v>
+        <v>59</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>56</v>
@@ -4807,40 +4741,40 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>298</v>
+        <v>118</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>300</v>
+        <v>185</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J84" s="3">
         <v>0</v>
@@ -4848,318 +4782,316 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J85" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>71</v>
+        <v>311</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>310</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J87" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J88" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J89" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>172</v>
+        <v>321</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J90" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J91" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>172</v>
+        <v>327</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>172</v>
+        <v>331</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="J93" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>126</v>
+        <v>333</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>213</v>
+        <v>335</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>63</v>
+        <v>337</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>189</v>
+        <v>338</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>38</v>
@@ -5169,40 +5101,42 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F96" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -5210,196 +5144,198 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>336</v>
+        <v>67</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J97" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>172</v>
+        <v>327</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J98" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="C99" s="3" t="s">
-        <v>213</v>
+        <v>349</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J99" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J100" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>344</v>
+        <v>53</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="J101" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>344</v>
+        <v>142</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>351</v>
+        <v>185</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F102" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="G102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J102" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>322</v>
+        <v>59</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>353</v>
+        <v>217</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>336</v>
+        <v>218</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>38</v>
@@ -5409,70 +5345,70 @@
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J103" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>355</v>
+        <v>59</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>356</v>
+        <v>212</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="J104" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>74</v>
+        <v>360</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>360</v>
+        <v>164</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="J105" s="3">
         <v>1</v>
@@ -5480,29 +5416,29 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>363</v>
+        <v>255</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>186</v>
+        <v>364</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J106" s="3">
         <v>0</v>
@@ -5510,556 +5446,256 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>281</v>
+        <v>368</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J107" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>204</v>
+        <v>44</v>
       </c>
       <c r="J108" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>344</v>
+        <v>118</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>372</v>
+        <v>164</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J109" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F110" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>378</v>
+      </c>
       <c r="G110" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="J110" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F111" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>382</v>
+      </c>
       <c r="G111" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="J111" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>209</v>
+        <v>385</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>213</v>
+        <v>386</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F112" s="3"/>
+      <c r="F112" s="3" t="s">
+        <v>387</v>
+      </c>
       <c r="G112" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J112" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>344</v>
+        <v>389</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>277</v>
+        <v>391</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F113" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>392</v>
+      </c>
       <c r="G113" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J113" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>71</v>
+        <v>377</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>56</v>
+        <v>377</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F114" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>396</v>
+      </c>
       <c r="G114" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="J114" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J115" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J116" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J117" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J118" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J119" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J120" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J121" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J122" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="I123" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J123" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="I124" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J124" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J124"/>
+  <autoFilter ref="A1:J114"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6174,16 +5810,6 @@
     <hyperlink ref="H112" r:id="rId111"/>
     <hyperlink ref="H113" r:id="rId112"/>
     <hyperlink ref="H114" r:id="rId113"/>
-    <hyperlink ref="H115" r:id="rId114"/>
-    <hyperlink ref="H116" r:id="rId115"/>
-    <hyperlink ref="H117" r:id="rId116"/>
-    <hyperlink ref="H118" r:id="rId117"/>
-    <hyperlink ref="H119" r:id="rId118"/>
-    <hyperlink ref="H120" r:id="rId119"/>
-    <hyperlink ref="H121" r:id="rId120"/>
-    <hyperlink ref="H122" r:id="rId121"/>
-    <hyperlink ref="H123" r:id="rId122"/>
-    <hyperlink ref="H124" r:id="rId123"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6191,8 +5817,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -6225,13 +5851,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6239,18 +5865,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6258,18 +5884,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6277,18 +5903,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6296,18 +5922,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6315,18 +5941,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6334,18 +5960,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>233</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6353,18 +5979,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6372,18 +5998,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6391,18 +6017,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>332</v>
+        <v>265</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6410,18 +6036,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>333</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>362</v>
+        <v>271</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>363</v>
+        <v>272</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6429,18 +6055,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>364</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>344</v>
+        <v>59</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>371</v>
+        <v>294</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>372</v>
+        <v>164</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6448,18 +6074,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>373</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>374</v>
+        <v>59</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>375</v>
+        <v>301</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>376</v>
+        <v>176</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6467,18 +6093,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>377</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>228</v>
+        <v>303</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6486,11 +6112,239 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>397</v>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G27"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6506,6 +6360,18 @@
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
     <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
+    <hyperlink ref="G26" r:id="rId25"/>
+    <hyperlink ref="G27" r:id="rId26"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6519,127 +6385,127 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>423</v>
+        <v>241</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>255</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>310</v>
+        <v>403</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -6661,12 +6527,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -6682,23 +6548,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6706,7 +6572,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>303</v>
+        <v>255</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6714,7 +6580,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6722,7 +6588,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6730,7 +6596,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6738,7 +6604,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6746,7 +6612,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6754,7 +6620,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6762,7 +6628,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6770,7 +6636,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6778,7 +6644,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6799,16 +6665,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2">
@@ -6816,13 +6682,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3">
-        <v>25.9</v>
+        <v>18.5</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -6830,13 +6696,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
-        <v>18.5</v>
+        <v>15.6</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6844,13 +6710,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="D4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6858,7 +6724,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C5" s="3">
         <v>14.0</v>
@@ -6872,7 +6738,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C6" s="3">
         <v>11.3</v>
@@ -6886,7 +6752,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3">
         <v>7.2</v>
@@ -6900,10 +6766,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6914,10 +6780,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="C9" s="3">
-        <v>6.0</v>
+        <v>5.8</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6928,13 +6794,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>144</v>
+        <v>255</v>
       </c>
       <c r="C10" s="3">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6942,13 +6808,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6956,13 +6822,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>127</v>
+        <v>341</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6970,13 +6836,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6984,13 +6850,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>221</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6998,7 +6864,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -7012,13 +6878,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>399</v>
+        <v>217</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7038,32 +6904,32 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4">
@@ -7071,10 +6937,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -7093,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
@@ -7101,15 +6967,15 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -7117,20 +6983,20 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -7138,7 +7004,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="B7" s="3">
         <v>4</v>
@@ -7146,7 +7012,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -7154,7 +7020,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -7162,7 +7028,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -7189,10 +7055,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7204,10 +7070,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -7224,28 +7090,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7256,31 +7122,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>362</v>
+        <v>430</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="F3" s="3">
         <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4">
@@ -7288,31 +7154,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F4" s="3">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5">
@@ -7320,31 +7186,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>462</v>
+        <v>255</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>172</v>
+        <v>439</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
@@ -7352,28 +7218,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>380</v>
+        <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F6" s="3">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -7384,31 +7250,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="F7" s="3">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>79</v>
+        <v>449</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
@@ -7416,31 +7282,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>471</v>
+        <v>430</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>472</v>
+        <v>292</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="F8" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
@@ -7448,31 +7314,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>151</v>
+        <v>453</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>152</v>
+        <v>454</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
@@ -7480,28 +7346,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7512,28 +7378,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>463</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>464</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7544,31 +7410,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>485</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>287</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>487</v>
+        <v>73</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -7576,31 +7442,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -7608,28 +7474,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>492</v>
+        <v>143</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7640,31 +7506,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>496</v>
+        <v>210</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F15" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -7672,28 +7538,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>172</v>
+        <v>481</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F16" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7704,28 +7570,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>504</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7736,28 +7602,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7768,31 +7634,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20">
@@ -7800,28 +7666,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>517</v>
+        <v>164</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -7832,31 +7698,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>362</v>
+        <v>472</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="521">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-21T09:59:32</t>
+    <t xml:space="preserve">2026-05-22T09:45:50</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -216,1215 +216,1161 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Delivery Engineer</t>
+    <t xml:space="preserve">AI Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7818160&amp;gh_jid=7818160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of AI Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontend Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-7635287?gh_jid=7635287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Helm, Istio, Service Mesh, Security, Argo CD, Observability, Karpenter, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8323401002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineering (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Group Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4415902208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4413396534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFTECH-IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T&amp;S Talents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majestic Labs ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-majestic-labs-ai-4416325504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playermaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LayerX Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Frequency System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-milestone-systems-4416490430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electreon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMware &amp; VDI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-vdi-infrastructure-engineer-at-shavit-software-4416479932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4412256259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freightos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpressVPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering Manager - SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipalti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chief Technology Officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access Softek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-chief-technology-officer-access-softek-1131633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudlinux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform, Ansible, CI/CD, Linux, Grafana, Postgres, MongoDB, Redis, Networking, Security, Observability, OpenTofu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-senior-database-reliability-engineer-cloudlinux-1131613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevRel Content Creator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperPlane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, CI/CD, Lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-devrel-content-creator-superplane-1131594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HighLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP, Go, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-staff-engineer-platform-engineering-highlevel-1131588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kafka, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-manager-platform-engineering-natera-1131552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager AI Fleet Management &amp;amp; Honk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spotify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-engineering-manager-ai-fleet-management-amp-honk-spotify-1131520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">Payoneer</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, CI/CD, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7861540/?gh_jid=7861540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Security</t>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, ELK/Elastic, Vault, Postgres, MongoDB, Kafka, RabbitMQ, Networking, Security, Argo CD, Observability, Flux/GitOps, Snyk/Sec Scanning, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7765451/?gh_jid=7765451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7818160&amp;gh_jid=7818160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of AI Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frontend Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-7635287?gh_jid=7635287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Helm, Istio, Service Mesh, Security, Argo CD, Observability, Karpenter, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8323401002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Group Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4415902208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Majestic Labs ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-majestic-labs-ai-4416325504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4413396534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFTECH-IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SailPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T&amp;S Talents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4408668742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4416232991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior VMware &amp; VDI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-vmware-vdi-infrastructure-engineer-at-extreme-4416018203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – UAV Systems Development &amp; Integration (Aerospace)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GroWings Robotx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kadima, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-uav-systems-development-integration-aerospace-at-growings-robotx-4410552923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Frequency System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-system-engineer-at-ge-healthcare-4398024249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-milestone-systems-4416490430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-phy-system-engineer-at-nvidia-ai-4413348316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22490 - System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware &amp; VDI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-vdi-infrastructure-engineer-at-shavit-software-4416479932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freightos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering Manager - SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipalti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudlinux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform, Ansible, CI/CD, Linux, Grafana, Postgres, MongoDB, Redis, Networking, Security, Observability, OpenTofu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-senior-database-reliability-engineer-cloudlinux-1131613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevRel Content Creator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperPlane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, CI/CD, Lambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-devrel-content-creator-superplane-1131594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HighLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Go, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-staff-engineer-platform-engineering-highlevel-1131588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafka, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-manager-platform-engineering-natera-1131552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager AI Fleet Management &amp;amp; Honk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spotify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-engineering-manager-ai-fleet-management-amp-honk-spotify-1131520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator (36311)</t>
   </si>
   <si>
@@ -1494,18 +1440,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
@@ -1518,13 +1452,76 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
   </si>
   <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control-M System Administrator 3047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isracard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/control-m-system-administrator-3047-at-isracard-4405630305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier II III UC Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTEC Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyderabad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-tier-ii-iii-uc-support-engineer-ttec-digital-1131561</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
@@ -1539,25 +1536,25 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform/IaC</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1709,7 +1706,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -1717,7 +1714,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1725,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -1733,7 +1730,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1805,7 +1802,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -1813,7 +1810,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -1821,7 +1818,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1840,36 +1837,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>427</v>
+        <v>501</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>502</v>
+        <v>421</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1877,7 +1874,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1896,15 +1893,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B2" s="3">
         <v>28</v>
@@ -1912,95 +1909,95 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>410</v>
+        <v>189</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>506</v>
+        <v>404</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>507</v>
+        <v>399</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>405</v>
+        <v>505</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>196</v>
+        <v>506</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>510</v>
+        <v>395</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>401</v>
+        <v>509</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -2008,7 +2005,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>512</v>
+        <v>398</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -2016,7 +2013,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>404</v>
+        <v>511</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -2044,13 +2041,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="2">
@@ -2058,13 +2055,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2076,25 +2073,25 @@
         <v>77</v>
       </c>
       <c r="C3" s="3">
-        <v>34.0</v>
+        <v>35.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2103,73 +2100,73 @@
         <v>24</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>38.4</v>
+        <v>33.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.4</v>
+        <v>23.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>7.9</v>
+        <v>7.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2253,7 +2250,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2285,7 +2282,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2317,7 +2314,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2347,7 +2344,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2379,7 +2376,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2411,7 +2408,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2443,7 +2440,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2475,7 +2472,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2492,27 +2489,27 @@
         <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>66</v>
@@ -2524,7 +2521,7 @@
         <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>72</v>
@@ -2536,15 +2533,15 @@
         <v>73</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>66</v>
@@ -2556,257 +2553,257 @@
         <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J16" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J18" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>56</v>
@@ -2815,27 +2812,27 @@
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J20" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>56</v>
@@ -2844,43 +2841,41 @@
         <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>111</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
@@ -2891,7 +2886,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -2905,33 +2900,33 @@
         <v>115</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>56</v>
@@ -2940,30 +2935,30 @@
         <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>56</v>
@@ -2972,63 +2967,65 @@
         <v>56</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>56</v>
@@ -3037,39 +3034,39 @@
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
@@ -3081,7 +3078,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -3089,42 +3086,42 @@
         <v>135</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>56</v>
@@ -3133,224 +3130,218 @@
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>148</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J32" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>151</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J33" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="I34" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J34" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3363,24 +3354,24 @@
         <v>166</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
@@ -3393,12 +3384,12 @@
         <v>169</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>170</v>
@@ -3410,7 +3401,7 @@
         <v>172</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3420,15 +3411,15 @@
         <v>173</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="J39" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>175</v>
@@ -3440,7 +3431,7 @@
         <v>56</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
@@ -3450,7 +3441,7 @@
         <v>177</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="J40" s="3">
         <v>4</v>
@@ -3458,19 +3449,19 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
@@ -3480,27 +3471,27 @@
         <v>181</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>182</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3510,27 +3501,27 @@
         <v>183</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3540,10 +3531,10 @@
         <v>186</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -3554,15 +3545,17 @@
         <v>188</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
@@ -3570,10 +3563,10 @@
         <v>190</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -3584,23 +3577,23 @@
         <v>192</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="J45" s="3">
         <v>2</v>
@@ -3608,23 +3601,21 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
@@ -3632,97 +3623,97 @@
         <v>197</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="J49" s="3">
         <v>4</v>
@@ -3730,169 +3721,169 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>218</v>
+        <v>176</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>219</v>
+        <v>56</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D55" s="3" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3902,37 +3893,37 @@
         <v>222</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="J56" s="3">
         <v>1</v>
@@ -3940,43 +3931,43 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="J57" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>56</v>
@@ -3989,54 +3980,54 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>169</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>56</v>
@@ -4049,27 +4040,27 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -4079,72 +4070,70 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>176</v>
+        <v>247</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>241</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J63" s="3">
         <v>0</v>
@@ -4152,133 +4141,133 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>243</v>
+        <v>106</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>246</v>
+        <v>106</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>248</v>
+        <v>171</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>250</v>
+        <v>106</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>252</v>
+        <v>171</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J66" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>258</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>56</v>
@@ -4294,10 +4283,10 @@
         <v>259</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4308,383 +4297,383 @@
         <v>261</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>266</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D71" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>271</v>
+        <v>59</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>274</v>
+        <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J74" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>219</v>
+        <v>116</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="J77" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="J78" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>164</v>
+        <v>277</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="J81" s="3">
         <v>2</v>
@@ -4692,29 +4681,29 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>118</v>
+        <v>295</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="J82" s="3">
         <v>4</v>
@@ -4722,79 +4711,79 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>118</v>
+        <v>289</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>185</v>
+        <v>302</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
@@ -4804,7 +4793,7 @@
         <v>306</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4815,46 +4804,46 @@
         <v>307</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>164</v>
+        <v>308</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>169</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
@@ -4864,10 +4853,10 @@
         <v>312</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4878,43 +4867,43 @@
         <v>314</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>185</v>
+        <v>315</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>317</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
@@ -4924,10 +4913,10 @@
         <v>318</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4938,15 +4927,17 @@
         <v>320</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
@@ -4954,10 +4945,10 @@
         <v>322</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="J90" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4968,73 +4959,73 @@
         <v>324</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>67</v>
+        <v>325</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>331</v>
+        <v>156</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
@@ -5044,10 +5035,10 @@
         <v>332</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -5058,23 +5049,23 @@
         <v>334</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="J94" s="3">
         <v>4</v>
@@ -5082,29 +5073,29 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="D95" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J95" s="3">
         <v>0</v>
@@ -5112,13 +5103,13 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>341</v>
+        <v>232</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>56</v>
@@ -5126,37 +5117,35 @@
       <c r="E96" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>241</v>
-      </c>
+      <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D97" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
@@ -5166,81 +5155,83 @@
         <v>344</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="J97" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>347</v>
-      </c>
       <c r="I98" s="3" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="J98" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>348</v>
+        <v>53</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>349</v>
+        <v>156</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>56</v>
@@ -5253,24 +5244,24 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>354</v>
+        <v>201</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>56</v>
@@ -5283,59 +5274,57 @@
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J101" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>142</v>
+        <v>353</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>241</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="J102" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>218</v>
+        <v>357</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>219</v>
+        <v>116</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>38</v>
@@ -5348,97 +5337,99 @@
         <v>358</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="J103" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>59</v>
+        <v>359</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>212</v>
+        <v>360</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="J104" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>360</v>
+        <v>106</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="J105" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>255</v>
+        <v>365</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F106" s="3"/>
+      <c r="F106" s="3" t="s">
+        <v>368</v>
+      </c>
       <c r="G106" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J106" s="3">
         <v>0</v>
@@ -5446,256 +5437,166 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="D107" s="3" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F107" s="3"/>
+      <c r="F107" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="G107" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>210</v>
+        <v>367</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>56</v>
+        <v>367</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F108" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>376</v>
+      </c>
       <c r="G108" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="J108" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>118</v>
+        <v>378</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>164</v>
+        <v>380</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F109" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>381</v>
+      </c>
       <c r="G109" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>178</v>
+        <v>44</v>
       </c>
       <c r="J109" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="J110" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>178</v>
+        <v>41</v>
       </c>
       <c r="J111" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J112" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J113" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J114" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J114"/>
+  <autoFilter ref="A1:J111"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5807,9 +5708,6 @@
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
-    <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5818,7 +5716,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5851,13 +5749,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5865,18 +5763,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5884,18 +5782,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5903,18 +5801,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>207</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>266</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>164</v>
+        <v>268</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5922,18 +5820,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>153</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5941,18 +5839,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>179</v>
+        <v>304</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5960,18 +5858,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>230</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>233</v>
+        <v>289</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>234</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>210</v>
+        <v>337</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5979,18 +5877,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>235</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>239</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>240</v>
+        <v>354</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5998,353 +5896,30 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>242</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>254</v>
+        <v>364</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>255</v>
+        <v>365</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>210</v>
+        <v>366</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="3" t="s">
         <v>369</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6355,23 +5930,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
-    <hyperlink ref="G24" r:id="rId23"/>
-    <hyperlink ref="G25" r:id="rId24"/>
-    <hyperlink ref="G26" r:id="rId25"/>
-    <hyperlink ref="G27" r:id="rId26"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6385,47 +5943,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>241</v>
+        <v>321</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B6" s="3">
         <v>18</v>
@@ -6433,71 +5991,71 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6505,10 +6063,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6518,7 +6076,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6527,12 +6085,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -6548,7 +6106,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6556,15 +6114,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>66</v>
+        <v>232</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6572,15 +6130,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>255</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6588,7 +6146,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6596,7 +6154,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6604,7 +6162,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6612,7 +6170,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6620,7 +6178,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>212</v>
+        <v>320</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6628,26 +6186,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>217</v>
+        <v>54</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>223</v>
+        <v>93</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>287</v>
+        <v>97</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6658,23 +6216,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
@@ -6682,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3">
         <v>18.5</v>
@@ -6710,13 +6268,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3">
-        <v>15.1</v>
+        <v>14.0</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6724,13 +6282,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3">
-        <v>14.0</v>
+        <v>11.3</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6738,13 +6296,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="C6" s="3">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6752,10 +6310,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3">
-        <v>7.2</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6766,10 +6324,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0</v>
+        <v>5.8</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6780,13 +6338,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="C9" s="3">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -6794,13 +6352,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6808,13 +6366,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>195</v>
+        <v>107</v>
       </c>
       <c r="C11" s="3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6822,13 +6380,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>341</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6836,13 +6394,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6850,10 +6408,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>371</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -6864,10 +6422,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6878,10 +6436,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6904,32 +6462,32 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3">
         <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4">
@@ -6937,10 +6495,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6959,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2">
@@ -6967,15 +6525,15 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -6983,7 +6541,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -6996,7 +6554,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>367</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -7004,23 +6562,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>377</v>
+        <v>208</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -7028,7 +6586,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -7055,10 +6613,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7070,10 +6628,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -7090,28 +6648,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7122,31 +6680,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>430</v>
+        <v>310</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F3" s="3">
         <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
@@ -7154,31 +6712,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3">
+        <v>71</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="F4" s="3">
-        <v>84</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>437</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -7186,31 +6744,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>255</v>
+        <v>434</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>439</v>
+        <v>156</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F5" s="3">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -7218,28 +6776,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>164</v>
+        <v>343</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="F6" s="3">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -7250,31 +6808,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>200</v>
+        <v>443</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F7" s="3">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
@@ -7282,31 +6840,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>292</v>
+        <v>447</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F8" s="3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9">
@@ -7314,31 +6872,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F9" s="3">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="F9" s="3">
-        <v>60</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>456</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -7346,28 +6904,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>458</v>
+        <v>131</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="F10" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7378,28 +6936,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>464</v>
+        <v>176</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F11" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7410,31 +6968,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>461</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>462</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>463</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F12" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>73</v>
+        <v>465</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -7442,31 +7000,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F13" s="3">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="F13" s="3">
-        <v>48</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>471</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -7474,28 +7032,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F14" s="3">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F14" s="3">
-        <v>47</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7506,28 +7064,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" s="3">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F15" s="3">
-        <v>47</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7538,31 +7096,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F16" s="3">
+        <v>40</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F16" s="3">
-        <v>47</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17">
@@ -7570,28 +7128,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>481</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7602,28 +7160,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F18" s="3">
+        <v>36</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F18" s="3">
-        <v>44</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>490</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>44</v>
@@ -7634,31 +7192,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F19" s="3">
+        <v>36</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="F19" s="3">
-        <v>40</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -7666,31 +7224,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F20" s="3">
+        <v>34</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F20" s="3">
-        <v>40</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>498</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
@@ -7698,28 +7256,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F21" s="3">
+        <v>34</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F21" s="3">
-        <v>40</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>44</v>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-22T09:45:50</t>
+    <t xml:space="preserve">2026-05-24T08:42:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -252,16 +252,16 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
   </si>
   <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+    <t xml:space="preserve">GenAI Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security, Rust, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7939091&amp;gh_jid=7939091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
     <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
@@ -474,30 +474,111 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4415902208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medulla</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4415902208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">21936 - DevOps Engineer</t>
   </si>
   <si>
@@ -528,24 +609,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cellebrite-4401287628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
@@ -573,303 +636,258 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">DataTeam</t>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4418661285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T&amp;S Talents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dell-technologies-4417803326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
   </si>
   <si>
     <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4413396534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFTECH-IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-softech-il-4412092684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4415416940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T&amp;S Talents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Majestic Labs ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-majestic-labs-ai-4416325504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
   </si>
   <si>
@@ -888,66 +906,57 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Playermaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LayerX Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Frequency System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SerDes System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-serdes-system-engineer-at-altera-4415501735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbit Communication Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Infrastructure Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
   </si>
   <si>
@@ -960,55 +969,31 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-milestone-systems-4416490430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Yanai, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-electreon-4415179276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware &amp; VDI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-vdi-infrastructure-engineer-at-shavit-software-4416479932</t>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4412256259</t>
   </si>
   <si>
     <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
@@ -1020,46 +1005,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
   </si>
   <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4412256259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freightos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - AMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-ams-at-orbit-communication-systems-4418647930</t>
   </si>
   <si>
     <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
@@ -1077,6 +1032,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InspHire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
   </si>
   <si>
@@ -1107,10 +1080,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
   </si>
   <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+    <t xml:space="preserve">Lead DevOps Engineer (Bangkok based, relocation provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-bangkok-based-relocation-provided-at-agoda-4410065283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer (SRE) (Bangkok based, relocation provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-sre-bangkok-based-relocation-provided-at-agoda-4410060486</t>
   </si>
   <si>
     <t xml:space="preserve">Chief Technology Officer</t>
@@ -1131,115 +1113,49 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-chief-technology-officer-access-softek-1131633</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudlinux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform, Ansible, CI/CD, Linux, Grafana, Postgres, MongoDB, Redis, Networking, Security, Observability, OpenTofu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-senior-database-reliability-engineer-cloudlinux-1131613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevRel Content Creator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperPlane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, CI/CD, Lambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-devrel-content-creator-superplane-1131594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HighLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Go, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-staff-engineer-platform-engineering-highlevel-1131588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafka, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-manager-platform-engineering-natera-1131552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager AI Fleet Management &amp;amp; Honk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spotify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-engineering-manager-ai-fleet-management-amp-honk-spotify-1131520</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
     <t xml:space="preserve">Mentions</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
+    <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">Observability</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Terraform</t>
   </si>
   <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
+    <t xml:space="preserve">Prometheus</t>
   </si>
   <si>
     <t xml:space="preserve">Open Roles</t>
@@ -1263,10 +1179,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8%</t>
+    <t xml:space="preserve">57.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1332,7 +1248,7 @@
     <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
   </si>
   <si>
     <t xml:space="preserve">SAP ECC System Administrator</t>
@@ -1350,15 +1266,24 @@
     <t xml:space="preserve">IT Technician</t>
   </si>
   <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator (36311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4416210373</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Corp System Administrator</t>
   </si>
   <si>
@@ -1368,19 +1293,7 @@
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4416210373</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-corp-system-administrator-at-payoneer-4416274281</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist</t>
@@ -1392,6 +1305,21 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
@@ -1404,21 +1332,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Technical Support</t>
   </si>
   <si>
@@ -1461,6 +1374,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
   </si>
   <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
+  </si>
+  <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
   </si>
   <si>
@@ -1485,18 +1419,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/control-m-system-administrator-3047-at-isracard-4405630305</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
     <t xml:space="preserve">Information Technology Help Desk</t>
   </si>
   <si>
@@ -1509,21 +1431,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier II III UC Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTEC Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyderabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-tier-ii-iii-uc-support-engineer-ttec-digital-1131561</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -1536,19 +1443,19 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
+    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
@@ -1706,7 +1613,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -1714,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1722,7 +1629,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1730,7 +1637,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -1818,7 +1725,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1837,28 +1744,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
@@ -1866,7 +1773,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1874,7 +1781,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1893,87 +1800,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>399</v>
+        <v>474</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>505</v>
+        <v>475</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>506</v>
+        <v>371</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>508</v>
+        <v>366</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -1981,7 +1888,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>395</v>
+        <v>477</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -1989,15 +1896,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -2005,7 +1912,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -2013,10 +1920,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2041,13 +1948,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>514</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
@@ -2058,10 +1965,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>16.1</v>
+        <v>14.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2070,28 +1977,28 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>35.6</v>
+        <v>33.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2100,73 +2007,73 @@
         <v>24</v>
       </c>
       <c r="B5" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.2</v>
+        <v>31.4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>23.9</v>
+        <v>20.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>519</v>
+        <v>488</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.8</v>
+        <v>13.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>520</v>
+        <v>489</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>7.0</v>
+        <v>6.7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2179,7 +2086,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2250,7 +2157,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2282,7 +2189,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2314,7 +2221,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2344,7 +2251,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -2376,7 +2283,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2408,7 +2315,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2440,7 +2347,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2472,7 +2379,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -2504,7 +2411,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -2536,7 +2443,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -2568,7 +2475,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -2579,7 +2486,7 @@
         <v>66</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>56</v>
@@ -2588,19 +2495,19 @@
         <v>71</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J13" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2632,7 +2539,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -2664,7 +2571,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -2696,7 +2603,7 @@
         <v>44</v>
       </c>
       <c r="J16" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2728,7 +2635,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2760,7 +2667,7 @@
         <v>96</v>
       </c>
       <c r="J18" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2792,7 +2699,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -2824,7 +2731,7 @@
         <v>96</v>
       </c>
       <c r="J20" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -2856,7 +2763,7 @@
         <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2886,7 +2793,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -2918,7 +2825,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -2950,7 +2857,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -2982,7 +2889,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -3014,7 +2921,7 @@
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -3046,7 +2953,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -3078,7 +2985,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -3110,7 +3017,7 @@
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -3142,7 +3049,7 @@
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -3174,7 +3081,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -3204,7 +3111,7 @@
         <v>44</v>
       </c>
       <c r="J32" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -3234,7 +3141,7 @@
         <v>44</v>
       </c>
       <c r="J33" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -3248,7 +3155,7 @@
         <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>71</v>
@@ -3264,24 +3171,24 @@
         <v>154</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
@@ -3294,21 +3201,21 @@
         <v>158</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>71</v>
@@ -3318,57 +3225,57 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>71</v>
@@ -3378,13 +3285,13 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -3392,13 +3299,13 @@
         <v>106</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>71</v>
@@ -3408,10 +3315,10 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="J39" s="3">
         <v>5</v>
@@ -3419,13 +3326,13 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>56</v>
@@ -3438,24 +3345,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>116</v>
@@ -3463,18 +3370,20 @@
       <c r="E41" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="J41" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -3482,10 +3391,10 @@
         <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>56</v>
@@ -3498,10 +3407,10 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3509,13 +3418,13 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>116</v>
@@ -3528,10 +3437,10 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J43" s="3">
         <v>3</v>
@@ -3539,23 +3448,21 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
@@ -3566,21 +3473,21 @@
         <v>96</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>71</v>
@@ -3590,10 +3497,10 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="J45" s="3">
         <v>2</v>
@@ -3601,16 +3508,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>195</v>
+        <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>71</v>
@@ -3620,24 +3527,24 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>158</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>56</v>
@@ -3650,27 +3557,27 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>71</v>
@@ -3683,10 +3590,10 @@
         <v>202</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3697,7 +3604,7 @@
         <v>203</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>56</v>
@@ -3710,13 +3617,13 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>96</v>
+        <v>193</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3724,13 +3631,13 @@
         <v>106</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>208</v>
+        <v>56</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>71</v>
@@ -3740,27 +3647,27 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>210</v>
+        <v>106</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>71</v>
@@ -3770,27 +3677,27 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>71</v>
@@ -3803,27 +3710,27 @@
         <v>214</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3833,21 +3740,21 @@
         <v>216</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>56</v>
@@ -3860,13 +3767,13 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>154</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3874,13 +3781,13 @@
         <v>106</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>71</v>
@@ -3890,114 +3797,114 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
@@ -4010,24 +3917,24 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>56</v>
@@ -4040,10 +3947,10 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J60" s="3">
         <v>3</v>
@@ -4051,16 +3958,16 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>239</v>
+        <v>152</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -4070,27 +3977,27 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>71</v>
@@ -4100,24 +4007,24 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="J62" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>247</v>
+        <v>152</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>56</v>
@@ -4130,10 +4037,10 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="J63" s="3">
         <v>0</v>
@@ -4141,106 +4048,106 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>106</v>
+        <v>239</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>106</v>
+        <v>242</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>71</v>
@@ -4250,10 +4157,10 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="J67" s="3">
         <v>4</v>
@@ -4261,16 +4168,16 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4280,10 +4187,10 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J68" s="3">
         <v>3</v>
@@ -4291,13 +4198,13 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>56</v>
@@ -4310,57 +4217,57 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="J69" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>263</v>
+        <v>59</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>268</v>
+        <v>188</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>71</v>
@@ -4370,84 +4277,84 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>59</v>
+        <v>264</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>53</v>
+        <v>267</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>274</v>
+        <v>59</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>56</v>
@@ -4460,54 +4367,54 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>279</v>
+        <v>106</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
@@ -4520,27 +4427,27 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J76" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>71</v>
@@ -4550,24 +4457,24 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>204</v>
+        <v>281</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>56</v>
@@ -4580,24 +4487,24 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>59</v>
+        <v>283</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>247</v>
+        <v>152</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
@@ -4610,27 +4517,27 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>71</v>
@@ -4640,27 +4547,27 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>96</v>
+        <v>193</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>293</v>
+        <v>208</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>71</v>
@@ -4670,24 +4577,24 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>158</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>295</v>
+        <v>59</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>56</v>
@@ -4700,57 +4607,59 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>96</v>
+        <v>185</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>300</v>
-      </c>
       <c r="I83" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>71</v>
@@ -4760,40 +4669,40 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4801,16 +4710,16 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>246</v>
+        <v>306</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>308</v>
+        <v>188</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>71</v>
@@ -4820,24 +4729,24 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>152</v>
+        <v>309</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>116</v>
@@ -4850,27 +4759,27 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>71</v>
@@ -4880,24 +4789,24 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>158</v>
       </c>
       <c r="J88" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>302</v>
+        <v>177</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>116</v>
@@ -4910,86 +4819,84 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>154</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>320</v>
+        <v>257</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>176</v>
+        <v>304</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>56</v>
+        <v>213</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>321</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="J91" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>116</v>
@@ -5002,24 +4909,24 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>56</v>
@@ -5032,27 +4939,27 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J93" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>302</v>
+        <v>212</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>71</v>
@@ -5062,27 +4969,27 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J94" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>337</v>
+        <v>188</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>71</v>
@@ -5092,10 +4999,10 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="J95" s="3">
         <v>0</v>
@@ -5103,13 +5010,13 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>339</v>
+        <v>53</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>232</v>
+        <v>332</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>56</v>
@@ -5122,89 +5029,87 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>154</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>96</v>
+        <v>185</v>
       </c>
       <c r="J97" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>130</v>
+        <v>337</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>321</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="J98" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>53</v>
+        <v>340</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>56</v>
+        <v>213</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>38</v>
@@ -5214,24 +5119,24 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J99" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>349</v>
+        <v>59</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>350</v>
+        <v>205</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>56</v>
@@ -5244,24 +5149,24 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>154</v>
       </c>
       <c r="J100" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>59</v>
+        <v>344</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>201</v>
+        <v>345</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>56</v>
@@ -5274,10 +5179,10 @@
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="J101" s="3">
         <v>2</v>
@@ -5285,16 +5190,16 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>354</v>
+        <v>240</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>156</v>
+        <v>348</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>38</v>
@@ -5304,299 +5209,139 @@
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>232</v>
+        <v>351</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>357</v>
+        <v>197</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="J103" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J104" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>106</v>
+        <v>356</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="J105" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="J106" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J107" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J108" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J109" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J110" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J111" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J111"/>
+  <autoFilter ref="A1:J106"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5703,11 +5448,6 @@
     <hyperlink ref="H104" r:id="rId103"/>
     <hyperlink ref="H105" r:id="rId104"/>
     <hyperlink ref="H106" r:id="rId105"/>
-    <hyperlink ref="H107" r:id="rId106"/>
-    <hyperlink ref="H108" r:id="rId107"/>
-    <hyperlink ref="H109" r:id="rId108"/>
-    <hyperlink ref="H110" r:id="rId109"/>
-    <hyperlink ref="H111" r:id="rId110"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5716,7 +5456,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5749,32 +5489,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5782,18 +5522,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>245</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5801,18 +5541,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>266</v>
+        <v>106</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>268</v>
+        <v>152</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5820,18 +5560,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>281</v>
+        <v>220</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>282</v>
+        <v>221</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5839,18 +5579,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>283</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>305</v>
+        <v>215</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5858,18 +5598,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>306</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>336</v>
+        <v>246</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>337</v>
+        <v>152</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5877,18 +5617,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>338</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5896,30 +5636,182 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>355</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>364</v>
+        <v>106</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>365</v>
+        <v>280</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>366</v>
+        <v>281</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>369</v>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G18"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5930,6 +5822,14 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5943,63 +5843,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>394</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>395</v>
+        <v>367</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -6007,7 +5907,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="B9" s="3">
         <v>14</v>
@@ -6015,7 +5915,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -6023,23 +5923,23 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -6047,7 +5947,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -6055,18 +5955,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6076,7 +5976,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6085,7 +5985,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>407</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -6114,7 +6014,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6154,7 +6054,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6162,7 +6062,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6170,7 +6070,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6178,7 +6078,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>320</v>
+        <v>215</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6186,26 +6086,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>93</v>
+        <v>240</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6223,16 +6123,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>407</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -6338,7 +6238,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="C9" s="3">
         <v>4.8</v>
@@ -6352,13 +6252,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>320</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -6366,10 +6266,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -6380,13 +6280,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6394,7 +6294,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6408,13 +6308,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>371</v>
+        <v>211</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6422,7 +6322,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6436,7 +6336,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6462,21 +6362,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -6484,10 +6384,10 @@
         <v>71</v>
       </c>
       <c r="B3" s="3">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>414</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
@@ -6495,10 +6395,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>415</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -6517,7 +6417,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -6525,7 +6425,7 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -6533,12 +6433,12 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -6546,7 +6446,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6554,7 +6454,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>367</v>
+        <v>161</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -6562,23 +6462,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6586,7 +6486,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>146</v>
+        <v>361</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -6613,10 +6513,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6628,10 +6528,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6648,28 +6548,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6680,31 +6580,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>424</v>
+        <v>396</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="F3" s="3">
         <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
@@ -6712,28 +6612,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F4" s="3">
         <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>44</v>
@@ -6744,31 +6644,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>156</v>
+        <v>304</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="F5" s="3">
         <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
@@ -6776,28 +6676,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="F6" s="3">
         <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -6808,31 +6708,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>443</v>
+        <v>215</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F7" s="3">
         <v>51</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8">
@@ -6840,31 +6740,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="F8" s="3">
         <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
@@ -6872,31 +6772,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>450</v>
+        <v>421</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="F9" s="3">
         <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -6904,7 +6804,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>131</v>
@@ -6913,19 +6813,19 @@
         <v>132</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>456</v>
+        <v>427</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -6936,28 +6836,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>176</v>
+        <v>430</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>459</v>
+        <v>431</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -6968,28 +6868,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>463</v>
+        <v>197</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -7000,7 +6900,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>35</v>
@@ -7009,19 +6909,19 @@
         <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F13" s="3">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7032,28 +6932,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>470</v>
+        <v>441</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>472</v>
+        <v>443</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -7064,28 +6964,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F15" s="3">
         <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>476</v>
+        <v>447</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7096,31 +6996,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F16" s="3">
         <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17">
@@ -7128,28 +7028,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>480</v>
+        <v>425</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>44</v>
@@ -7160,31 +7060,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>484</v>
+        <v>400</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>152</v>
+        <v>455</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19">
@@ -7192,28 +7092,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>489</v>
+        <v>459</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="F19" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>44</v>
@@ -7224,31 +7124,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>493</v>
+        <v>463</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -7256,31 +7156,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>498</v>
+        <v>212</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F21" s="3">
         <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>499</v>
+        <v>468</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>500</v>
+        <v>469</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24T08:42:35</t>
+    <t xml:space="preserve">2026-05-24T09:31:45</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -510,792 +510,738 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שני נוי - ייעוץ תעסוקתי</t>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T&amp;S Talents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-%D7%A9%D7%A0%D7%99-%D7%A0%D7%95%D7%99-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%AA%D7%A2%D7%A1%D7%95%D7%A7%D7%AA%D7%99-4412671581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure / DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dell-technologies-4417803326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415730614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playermaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LayerX Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoCompany1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418656632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Frequency System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-ge-healthcare-4398020443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InspHire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpressVPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chief Technology Officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access Softek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-chief-technology-officer-access-softek-1131633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-specialist-at-extreme-4416028315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4418661285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T&amp;S Talents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dell Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dell-technologies-4417803326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SerDes System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-serdes-system-engineer-at-altera-4415501735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
   </si>
   <si>
     <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4412256259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - AMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-ams-at-orbit-communication-systems-4418647930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InspHire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering Manager - SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipalti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead DevOps Engineer (Bangkok based, relocation provided)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-bangkok-based-relocation-provided-at-agoda-4410065283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead DevOps Engineer (SRE) (Bangkok based, relocation provided)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-sre-bangkok-based-relocation-provided-at-agoda-4410060486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chief Technology Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access Softek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-chief-technology-officer-access-softek-1131633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4416210373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-corp-system-administrator-at-payoneer-4416274281</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
@@ -1305,6 +1251,18 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -1320,18 +1278,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Technical Support</t>
   </si>
   <si>
@@ -1407,28 +1353,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
   </si>
   <si>
-    <t xml:space="preserve">Control-M System Administrator 3047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isracard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/control-m-system-administrator-3047-at-isracard-4405630305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
@@ -1449,16 +1383,16 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -1613,7 +1547,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1621,7 +1555,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1629,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -1637,7 +1571,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -1709,7 +1643,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1744,36 +1678,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>470</v>
+        <v>373</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>393</v>
+        <v>448</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1781,7 +1715,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1800,39 +1734,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>473</v>
+        <v>357</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>178</v>
+        <v>451</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -1840,31 +1774,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>377</v>
+        <v>452</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>474</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>475</v>
+        <v>350</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>371</v>
+        <v>453</v>
       </c>
       <c r="B9" s="3">
         <v>14</v>
@@ -1872,15 +1806,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>366</v>
+        <v>455</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -1888,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -1896,15 +1830,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>478</v>
+        <v>345</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1912,7 +1846,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>370</v>
+        <v>458</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -1920,10 +1854,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>480</v>
+        <v>349</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1948,13 +1882,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2">
@@ -1965,10 +1899,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>14.1</v>
+        <v>12.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1977,28 +1911,28 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3">
-        <v>33.0</v>
+        <v>35.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2010,70 +1944,70 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.4</v>
+        <v>30.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.0</v>
+        <v>18.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2084,7 +2018,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -3242,34 +3176,34 @@
         <v>164</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J37" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>160</v>
@@ -3285,7 +3219,7 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>158</v>
@@ -3296,16 +3230,16 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>71</v>
@@ -3315,24 +3249,24 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>56</v>
@@ -3345,7 +3279,7 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>80</v>
@@ -3356,13 +3290,13 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>116</v>
@@ -3370,20 +3304,18 @@
       <c r="E41" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>178</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -3391,13 +3323,13 @@
         <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>71</v>
@@ -3407,27 +3339,27 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>71</v>
@@ -3440,24 +3372,24 @@
         <v>184</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>71</v>
@@ -3467,13 +3399,13 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -3481,13 +3413,13 @@
         <v>106</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>71</v>
@@ -3497,13 +3429,13 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -3511,13 +3443,13 @@
         <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>71</v>
@@ -3527,27 +3459,27 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>71</v>
@@ -3557,27 +3489,27 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>199</v>
+        <v>106</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>71</v>
@@ -3587,13 +3519,13 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3601,7 +3533,7 @@
         <v>106</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>152</v>
@@ -3617,111 +3549,111 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>106</v>
+        <v>203</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>210</v>
+        <v>59</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>213</v>
+        <v>56</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>152</v>
@@ -3730,28 +3662,28 @@
         <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>152</v>
@@ -3767,27 +3699,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>213</v>
+        <v>56</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>71</v>
@@ -3797,147 +3729,147 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="D60" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3950,7 +3882,7 @@
         <v>232</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J60" s="3">
         <v>3</v>
@@ -3958,40 +3890,40 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>141</v>
+        <v>233</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>152</v>
@@ -4000,14 +3932,14 @@
         <v>56</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>44</v>
@@ -4018,13 +3950,13 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>56</v>
@@ -4037,24 +3969,24 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>56</v>
@@ -4067,37 +3999,37 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>158</v>
@@ -4108,46 +4040,46 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>71</v>
@@ -4157,54 +4089,54 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>253</v>
+        <v>201</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="C69" s="3" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>56</v>
@@ -4217,30 +4149,30 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="J69" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D70" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
@@ -4250,54 +4182,54 @@
         <v>260</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="J70" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D72" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>71</v>
@@ -4310,24 +4242,24 @@
         <v>266</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="J72" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>71</v>
@@ -4337,30 +4269,30 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="J73" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>59</v>
+        <v>269</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
@@ -4370,64 +4302,66 @@
         <v>271</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>273</v>
+        <v>191</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>80</v>
@@ -4438,19 +4372,19 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>277</v>
+        <v>59</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>278</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
@@ -4460,24 +4394,24 @@
         <v>279</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="J77" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>106</v>
+        <v>280</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>281</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>71</v>
@@ -4490,10 +4424,10 @@
         <v>282</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -4504,43 +4438,43 @@
         <v>284</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>152</v>
+        <v>285</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
@@ -4550,10 +4484,10 @@
         <v>289</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -4564,10 +4498,10 @@
         <v>291</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>71</v>
@@ -4580,61 +4514,59 @@
         <v>292</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>59</v>
+        <v>283</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>293</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>165</v>
+        <v>294</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>296</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>197</v>
+        <v>297</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>297</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
@@ -4642,10 +4574,10 @@
         <v>298</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="J83" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -4653,13 +4585,13 @@
         <v>299</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>71</v>
@@ -4669,7 +4601,7 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>80</v>
@@ -4680,46 +4612,46 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>303</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>304</v>
+        <v>175</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>71</v>
@@ -4729,27 +4661,27 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>71</v>
@@ -4759,27 +4691,27 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>71</v>
@@ -4789,177 +4721,177 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J88" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J89" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>316</v>
+        <v>53</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>304</v>
+        <v>152</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>213</v>
+        <v>56</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J90" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>320</v>
+        <v>152</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="J91" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="J92" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>152</v>
+        <v>250</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>299</v>
+        <v>168</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>212</v>
+        <v>325</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>71</v>
@@ -4969,51 +4901,51 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>330</v>
+        <v>59</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>306</v>
+        <v>199</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>53</v>
+        <v>328</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>152</v>
@@ -5029,27 +4961,27 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="J96" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>335</v>
+        <v>217</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>152</v>
+        <v>332</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>38</v>
@@ -5059,10 +4991,10 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J97" s="3">
         <v>3</v>
@@ -5070,278 +5002,68 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="J98" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="G99" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>342</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J100" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J101" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J102" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J103" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J104" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J105" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J106" s="3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5441,13 +5163,6 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
-    <hyperlink ref="H105" r:id="rId104"/>
-    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5455,7 +5170,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -5508,7 +5223,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>156</v>
@@ -5522,7 +5237,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -5530,10 +5245,10 @@
         <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5541,18 +5256,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5560,18 +5275,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5579,15 +5294,15 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>152</v>
@@ -5598,18 +5313,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>245</v>
+        <v>106</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5617,18 +5332,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5636,18 +5351,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>106</v>
+        <v>290</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>281</v>
+        <v>195</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5655,7 +5370,7 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11">
@@ -5663,10 +5378,10 @@
         <v>299</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5674,18 +5389,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5693,18 +5408,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5712,18 +5427,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5731,87 +5446,11 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5826,10 +5465,6 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5843,15 +5478,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="B2" s="3">
         <v>23</v>
@@ -5859,7 +5494,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5867,7 +5502,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="B4" s="3">
         <v>19</v>
@@ -5875,7 +5510,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="B5" s="3">
         <v>17</v>
@@ -5883,7 +5518,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -5891,7 +5526,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
@@ -5899,7 +5534,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5907,15 +5542,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5923,7 +5558,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5931,7 +5566,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -5939,7 +5574,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5947,7 +5582,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5955,7 +5590,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5963,7 +5598,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5976,7 +5611,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5985,7 +5620,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
@@ -6014,7 +5649,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6030,23 +5665,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6054,7 +5689,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6062,7 +5697,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6070,7 +5705,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6078,7 +5713,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6086,7 +5721,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6094,18 +5729,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>240</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>306</v>
+        <v>93</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6123,16 +5758,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
@@ -6238,7 +5873,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="C9" s="3">
         <v>4.8</v>
@@ -6252,13 +5887,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="C10" s="3">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6266,13 +5901,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6280,13 +5915,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6294,13 +5929,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6308,10 +5943,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6322,10 +5957,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6336,7 +5971,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6362,21 +5997,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3">
@@ -6384,10 +6019,10 @@
         <v>71</v>
       </c>
       <c r="B3" s="3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4">
@@ -6398,7 +6033,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6417,7 +6052,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
@@ -6425,7 +6060,7 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -6433,12 +6068,12 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -6446,10 +6081,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>251</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -6457,15 +6092,15 @@
         <v>161</v>
       </c>
       <c r="B6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6486,7 +6121,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -6513,10 +6148,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6528,10 +6163,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6548,28 +6183,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>152</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6580,31 +6215,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="F3" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -6612,31 +6247,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>400</v>
+        <v>304</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="F4" s="3">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
@@ -6644,31 +6279,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>406</v>
+        <v>217</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>304</v>
+        <v>385</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>409</v>
+        <v>387</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
@@ -6676,28 +6311,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>320</v>
+        <v>152</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F6" s="3">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>44</v>
@@ -6708,31 +6343,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>414</v>
+        <v>376</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="F7" s="3">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
@@ -6740,31 +6375,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>417</v>
+        <v>304</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>418</v>
+        <v>190</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="F8" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9">
@@ -6772,31 +6407,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F9" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>423</v>
+        <v>400</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -6804,28 +6439,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>131</v>
+        <v>403</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>132</v>
+        <v>404</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -6836,28 +6471,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>429</v>
+        <v>131</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>430</v>
+        <v>132</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -6868,28 +6503,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -6900,28 +6535,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>415</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>416</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -6932,28 +6567,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>441</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -6964,28 +6599,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -6996,31 +6631,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F16" s="3">
         <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -7028,31 +6663,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F17" s="3">
         <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
@@ -7060,31 +6695,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>455</v>
+        <v>191</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F18" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -7092,31 +6727,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>458</v>
+        <v>388</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>152</v>
+        <v>437</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F19" s="3">
         <v>37</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
@@ -7124,28 +6759,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>44</v>
@@ -7156,31 +6791,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24T09:31:45</t>
+    <t xml:space="preserve">2026-05-24T12:23:23</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">0.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -93,1324 +96,1381 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seniority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Seen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Automation Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4860257101?gh_jid=4860257101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Quality Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4865603101?gh_jid=4865603101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4857059101?gh_jid=4857059101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Python, Prometheus, Grafana, Pulumi, Networking, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7911982?gh_jid=7911982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7818160&amp;gh_jid=7818160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of AI Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security, Rust, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7939091&amp;gh_jid=7939091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontend Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-7635287?gh_jid=7635287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Helm, Istio, Service Mesh, Security, Argo CD, Observability, Karpenter, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8323401002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineering (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Group Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4417800793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4418661285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T&amp;S Talents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4418652579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-cyberark-4203254670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playermaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoCompany1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418656632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Frequency System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbit Communication Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22490 - System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Hadarly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-hr-hadarly-4418671109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4414866213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InspHire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpressVPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering Manager (SRE Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipalti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-team-at-tipalti-4412578041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer (Bangkok based, relocation provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-bangkok-based-relocation-provided-at-agoda-4410065283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer (SRE) (Bangkok based, relocation provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-sre-bangkok-based-relocation-provided-at-agoda-4410060486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elapsed (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lever</t>
+  </si>
+  <si>
     <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seniority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Seen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Automation Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4860257101?gh_jid=4860257101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Quality Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4865603101?gh_jid=4865603101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4857059101?gh_jid=4857059101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Python, Prometheus, Grafana, Pulumi, Networking, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7911982?gh_jid=7911982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7818160&amp;gh_jid=7818160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of AI Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security, Rust, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7939091&amp;gh_jid=7939091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668081006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frontend Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-7635287?gh_jid=7635287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Helm, Istio, Service Mesh, Security, Argo CD, Observability, Karpenter, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8323401002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8432893002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx (DevOps) Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, CI/CD, Python, Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Group Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4415902208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4415468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T&amp;S Talents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-upstream-security-4416028554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dell Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dell-technologies-4417803326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415730614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playermaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LayerX Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-layerx-security-4416034525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoCompany1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418656632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Frequency System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-ge-healthcare-4398020443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413388545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InspHire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-insphire-4417582835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chief Technology Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access Softek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-chief-technology-officer-access-softek-1131633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elapsed (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lever</t>
   </si>
   <si>
     <t xml:space="preserve">alljobs</t>
@@ -1547,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
@@ -1555,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1563,7 +1623,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1571,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1595,7 +1655,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1604,26 +1664,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1632,34 +1692,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
         <v>32</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1678,28 +1730,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1707,7 +1759,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1715,7 +1767,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1734,15 +1786,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="B2" s="3">
         <v>28</v>
@@ -1750,39 +1802,39 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
@@ -1790,55 +1842,55 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>350</v>
+        <v>473</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>453</v>
+        <v>377</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1846,18 +1898,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>458</v>
+        <v>372</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1876,138 +1928,138 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
-        <v>35.9</v>
+        <v>35.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>483</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3">
         <v>0.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.6</v>
+        <v>299.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -2018,7 +2070,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -2050,7 +2102,7 @@
         <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>31</v>
@@ -2082,7 +2134,7 @@
         <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>40</v>
@@ -2114,7 +2166,7 @@
         <v>39</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>43</v>
@@ -2146,7 +2198,7 @@
         <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>47</v>
@@ -2176,7 +2228,7 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>49</v>
@@ -2208,7 +2260,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>52</v>
@@ -2240,7 +2292,7 @@
         <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>58</v>
@@ -2272,7 +2324,7 @@
         <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>62</v>
@@ -2304,7 +2356,7 @@
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>64</v>
@@ -2336,7 +2388,7 @@
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>69</v>
@@ -2368,7 +2420,7 @@
         <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>73</v>
@@ -2400,7 +2452,7 @@
         <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>76</v>
@@ -2432,7 +2484,7 @@
         <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>79</v>
@@ -2464,7 +2516,7 @@
         <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>83</v>
@@ -2496,7 +2548,7 @@
         <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>85</v>
@@ -2528,7 +2580,7 @@
         <v>88</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>89</v>
@@ -2560,7 +2612,7 @@
         <v>90</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>91</v>
@@ -2592,7 +2644,7 @@
         <v>94</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>95</v>
@@ -2624,7 +2676,7 @@
         <v>99</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>100</v>
@@ -2656,7 +2708,7 @@
         <v>104</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>105</v>
@@ -2688,7 +2740,7 @@
         <v>108</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>109</v>
@@ -2718,7 +2770,7 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>112</v>
@@ -2750,7 +2802,7 @@
         <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>118</v>
@@ -2782,7 +2834,7 @@
         <v>119</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>120</v>
@@ -2814,7 +2866,7 @@
         <v>119</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>122</v>
@@ -2846,7 +2898,7 @@
         <v>125</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>126</v>
@@ -2878,7 +2930,7 @@
         <v>128</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>129</v>
@@ -2910,7 +2962,7 @@
         <v>133</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>134</v>
@@ -2942,7 +2994,7 @@
         <v>136</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>137</v>
@@ -2974,7 +3026,7 @@
         <v>139</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>140</v>
@@ -3006,7 +3058,7 @@
         <v>142</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>143</v>
@@ -3036,7 +3088,7 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>147</v>
@@ -3066,7 +3118,7 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>150</v>
@@ -3089,14 +3141,14 @@
         <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>153</v>
@@ -3105,37 +3157,37 @@
         <v>154</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D35" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>157</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3143,56 +3195,56 @@
         <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J37" s="3">
         <v>5</v>
@@ -3200,29 +3252,29 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>167</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J38" s="3">
         <v>5</v>
@@ -3230,13 +3282,13 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>56</v>
@@ -3246,16 +3298,16 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>169</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3266,7 +3318,7 @@
         <v>170</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>56</v>
@@ -3276,46 +3328,46 @@
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>176</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -3323,59 +3375,59 @@
         <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J42" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3383,56 +3435,56 @@
         <v>106</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>186</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J45" s="3">
         <v>5</v>
@@ -3443,10 +3495,10 @@
         <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>56</v>
@@ -3456,136 +3508,136 @@
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>201</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>202</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3596,7 +3648,7 @@
         <v>204</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>56</v>
@@ -3606,13 +3658,13 @@
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>205</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="J51" s="3">
         <v>3</v>
@@ -3620,13 +3672,13 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
@@ -3636,117 +3688,117 @@
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="J54" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
@@ -3756,286 +3808,286 @@
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>152</v>
+        <v>222</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="J57" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D62" s="3" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>238</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="J62" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="C63" s="3" t="s">
-        <v>235</v>
+        <v>152</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J63" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>243</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J64" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="D65" s="3" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>246</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4046,23 +4098,23 @@
         <v>248</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>249</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="J66" s="3">
         <v>3</v>
@@ -4070,103 +4122,103 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>251</v>
+        <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>251</v>
+        <v>56</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="D69" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>257</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>56</v>
@@ -4176,27 +4228,27 @@
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>260</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>261</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>56</v>
@@ -4206,7 +4258,7 @@
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>262</v>
@@ -4215,260 +4267,258 @@
         <v>154</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>264</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>265</v>
+        <v>156</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>106</v>
+        <v>265</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="C74" s="3" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J74" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="I75" s="3" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>276</v>
+        <v>106</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>59</v>
+        <v>254</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>278</v>
+        <v>207</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="J77" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>251</v>
+        <v>116</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="J79" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>287</v>
+        <v>59</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>56</v>
@@ -4478,87 +4528,87 @@
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="J80" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>297</v>
+        <v>166</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>116</v>
@@ -4568,27 +4618,27 @@
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>37</v>
@@ -4598,10 +4648,10 @@
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>80</v>
@@ -4612,13 +4662,13 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>116</v>
@@ -4628,27 +4678,27 @@
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>175</v>
+        <v>303</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>116</v>
@@ -4658,13 +4708,13 @@
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="J86" s="3">
         <v>4</v>
@@ -4672,83 +4722,83 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>234</v>
+        <v>306</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>281</v>
+        <v>152</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>251</v>
+        <v>116</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J87" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>234</v>
+        <v>309</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>311</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>250</v>
+        <v>189</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>251</v>
+        <v>190</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>312</v>
@@ -4762,59 +4812,59 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>152</v>
+        <v>283</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>316</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>152</v>
+        <v>303</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>317</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="J91" s="3">
         <v>3</v>
@@ -4828,26 +4878,26 @@
         <v>319</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>320</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="J92" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -4858,67 +4908,69 @@
         <v>322</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>251</v>
+        <v>56</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="G93" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>168</v>
+        <v>325</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>59</v>
+        <v>329</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>56</v>
@@ -4928,142 +4980,470 @@
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>154</v>
       </c>
       <c r="J95" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="J96" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>332</v>
+        <v>237</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="J97" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J98" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>337</v>
+        <v>53</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>339</v>
+        <v>156</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>340</v>
+        <v>56</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J99" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H99" s="3" t="s">
+      <c r="B100" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="I99" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J99" s="3">
+      <c r="C100" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J101" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J102" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J103" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J104" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J105" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J106" s="3">
         <v>2</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J107" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J108" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J109" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J110" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J110"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5163,6 +5543,17 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5170,7 +5561,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -5196,7 +5587,7 @@
         <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>31</v>
@@ -5215,7 +5606,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>79</v>
@@ -5223,21 +5614,21 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
@@ -5245,212 +5636,421 @@
         <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>213</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>267</v>
+        <v>192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>277</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>291</v>
+        <v>229</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>299</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>285</v>
+        <v>152</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>283</v>
+        <v>106</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>322</v>
+        <v>272</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>323</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G25"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5465,6 +6065,17 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5478,23 +6089,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5502,7 +6113,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="B4" s="3">
         <v>19</v>
@@ -5510,7 +6121,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="B5" s="3">
         <v>17</v>
@@ -5518,7 +6129,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -5526,15 +6137,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5542,7 +6153,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5550,7 +6161,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5558,7 +6169,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5566,7 +6177,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -5574,7 +6185,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5582,7 +6193,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5590,7 +6201,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5598,7 +6209,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5620,7 +6231,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5641,15 +6252,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>131</v>
+        <v>229</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -5665,7 +6276,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5673,7 +6284,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5705,7 +6316,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5713,7 +6324,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5721,7 +6332,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5729,18 +6340,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>207</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5758,16 +6369,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5831,13 +6442,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c r="C6" s="3">
-        <v>7.2</v>
+        <v>8.0</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -5845,10 +6456,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C7" s="3">
-        <v>6.0</v>
+        <v>7.2</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5859,10 +6470,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -5873,13 +6484,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>234</v>
+        <v>124</v>
       </c>
       <c r="C9" s="3">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5887,7 +6498,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3">
         <v>4.2</v>
@@ -5901,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -5943,7 +6554,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -5957,7 +6568,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -5971,7 +6582,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5997,21 +6608,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -6019,10 +6630,10 @@
         <v>71</v>
       </c>
       <c r="B3" s="3">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -6030,10 +6641,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6052,7 +6663,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -6060,7 +6671,7 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -6068,7 +6679,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -6081,7 +6692,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -6089,18 +6700,18 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6116,14 +6727,6 @@
         <v>146</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6148,10 +6751,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6163,13 +6766,13 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>31</v>
@@ -6183,28 +6786,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6215,28 +6818,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>80</v>
@@ -6247,31 +6850,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="F4" s="3">
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -6279,31 +6882,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="F5" s="3">
         <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
@@ -6311,31 +6914,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>388</v>
+        <v>331</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>152</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F6" s="3">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>392</v>
+        <v>333</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7">
@@ -6343,31 +6946,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>201</v>
+        <v>414</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="F7" s="3">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -6375,31 +6978,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>304</v>
+        <v>400</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="F8" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9">
@@ -6407,31 +7010,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>397</v>
+        <v>331</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>398</v>
+        <v>272</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F9" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -6439,31 +7042,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="F10" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -6471,28 +7074,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>428</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -6503,28 +7106,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>191</v>
+        <v>434</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -6535,28 +7138,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="F13" s="3">
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -6567,28 +7170,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>441</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>44</v>
@@ -6599,28 +7202,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>423</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F15" s="3">
         <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -6631,28 +7234,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -6663,31 +7266,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F17" s="3">
         <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -6695,31 +7298,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>191</v>
+        <v>455</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>44</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19">
@@ -6727,31 +7330,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>437</v>
+        <v>156</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F19" s="3">
         <v>37</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>158</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -6759,31 +7362,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
@@ -6791,31 +7394,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W21.xlsx
+++ b/reports/devops-jobs-israel-2026-W21.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24T12:23:23</t>
+    <t xml:space="preserve">2026-05-24T13:15:52</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -474,43 +474,403 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4417800793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-specialist-at-unilink-ltd-4416227469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-datateam-4413396534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medulla</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4417303251</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-4m-analytics-4417800793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4397207961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-4415778530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4418661285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T&amp;S Talents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-paragon-4405920494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4413308519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arpeely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-k-health-4416238463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-cyberark-4203254670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
   </si>
   <si>
     <t xml:space="preserve">Devops Infra/cloud Engineer</t>
@@ -525,208 +885,163 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
   </si>
   <si>
-    <t xml:space="preserve">Perion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-perion-4409208285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-abra-4416122934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-silverfort-4387394139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-etoro-4397231167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4416419518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4417075990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4418664905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4418661285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead | Cloud &amp; AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T&amp;S Talents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-ai-infrastructure-at-t-s-talents-4412222567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4413631256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4412256259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Beer Sheva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-beer-sheva-at-dell-technologies-4417593597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playermaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoCompany1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418656632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Frequency System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbit Communication Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Infrastructure Engineer</t>
@@ -738,118 +1053,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
   </si>
   <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4418652579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4418658876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arpeely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-arpeely-4415910074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Markets (First Prudential Markets)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-fp-markets-first-prudential-markets-4413685576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPAYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-papaya-4403897471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-ai-4412815977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-cyberark-4203254670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-gotfriends-4414860109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4416050532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4400349454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - AMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-ams-at-orbit-communication-systems-4418647930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
   </si>
   <si>
     <t xml:space="preserve">Data Infrastructure Engineer</t>
@@ -858,177 +1092,9 @@
     <t xml:space="preserve">SQLink Group</t>
   </si>
   <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-sqlink-group-4416149987</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-moveo-source-4415499378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-paragon-4405920494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playermaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-playermaker-4412218860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoCompany1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-nocompany1-4417800644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4418656632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4413306131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-genecit-4413310856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Frequency System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aeronautical System Engineer – Unmanned Aerial Vehicles (Multirotor &amp; Fixed-Wing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aeronautical-system-engineer-%E2%80%93-unmanned-aerial-vehicles-multirotor-fixed-wing-at-airobotics-4417703931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-orbit-communication-systems-4405119457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-infrastructure-engineer-at-solaredge-technologies-4418682144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22490 - System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22490-system-engineer-at-qualitest-4415499214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-shavit-software-4416080940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Team Lead</t>
   </si>
   <si>
@@ -1062,12 +1128,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
   </si>
   <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4415781146</t>
-  </si>
-  <si>
     <t xml:space="preserve">InspHire</t>
   </si>
   <si>
@@ -1083,51 +1143,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4413322860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpressVPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-expressvpn-4377800457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering Manager (SRE Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipalti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-team-at-tipalti-4412578041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead DevOps Engineer (Bangkok based, relocation provided)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agoda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-bangkok-based-relocation-provided-at-agoda-4410065283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead DevOps Engineer (SRE) (Bangkok based, relocation provided)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-sre-bangkok-based-relocation-provided-at-agoda-4410060486</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1191,10 +1206,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1%</t>
+    <t xml:space="preserve">60.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1221,45 +1236,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
   </si>
   <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
@@ -1275,33 +1263,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1332,6 +1293,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
@@ -1353,6 +1323,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Technical Support</t>
   </si>
   <si>
@@ -1374,6 +1359,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
+  </si>
+  <si>
     <t xml:space="preserve">Port.io</t>
   </si>
   <si>
@@ -1383,6 +1389,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
   </si>
   <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
     <t xml:space="preserve">Regulus</t>
   </si>
   <si>
@@ -1395,16 +1413,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
   </si>
   <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
   </si>
   <si>
     <t xml:space="preserve">Information Technology Help Desk</t>
@@ -1425,6 +1443,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
   </si>
   <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -1443,16 +1470,19 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform/IaC</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1467,12 +1497,12 @@
     <t xml:space="preserve">yes</t>
   </si>
   <si>
+    <t xml:space="preserve">indeed_il</t>
+  </si>
+  <si>
     <t xml:space="preserve">lever</t>
   </si>
   <si>
-    <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
     <t xml:space="preserve">alljobs</t>
   </si>
   <si>
@@ -1480,9 +1510,6 @@
   </si>
   <si>
     <t xml:space="preserve">jobmaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glassdoor</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1634,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -1615,7 +1642,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1623,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1631,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -1703,7 +1730,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -1730,28 +1757,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1759,7 +1786,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1767,7 +1794,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1786,39 +1813,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -1826,47 +1853,47 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>472</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>377</v>
+        <v>482</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>474</v>
+        <v>376</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -1874,15 +1901,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>371</v>
+        <v>485</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -1890,26 +1917,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>477</v>
+        <v>379</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>372</v>
+        <v>486</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>373</v>
+        <v>487</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1934,13 +1961,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2">
@@ -1951,10 +1978,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1963,105 +1990,90 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
         <v>35.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>3.2</v>
+        <v>8.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.3</v>
+        <v>32.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>299.7</v>
+        <v>308.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E8" s="3"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="E9" s="3"/>
     </row>
   </sheetData>
 </worksheet>
@@ -3141,7 +3153,7 @@
         <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>71</v>
@@ -3151,13 +3163,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J34" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -3165,10 +3177,10 @@
         <v>106</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>56</v>
@@ -3181,7 +3193,7 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>80</v>
@@ -3192,16 +3204,16 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>71</v>
@@ -3211,13 +3223,13 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -3225,13 +3237,13 @@
         <v>106</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>71</v>
@@ -3241,27 +3253,27 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>71</v>
@@ -3274,24 +3286,24 @@
         <v>167</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>71</v>
@@ -3301,13 +3313,13 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J39" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -3315,10 +3327,10 @@
         <v>106</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>56</v>
@@ -3331,27 +3343,27 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>71</v>
@@ -3361,10 +3373,10 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J41" s="3">
         <v>4</v>
@@ -3375,13 +3387,13 @@
         <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>71</v>
@@ -3391,13 +3403,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="J42" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3405,13 +3417,13 @@
         <v>106</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>71</v>
@@ -3421,13 +3433,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -3435,13 +3447,13 @@
         <v>106</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>71</v>
@@ -3454,24 +3466,24 @@
         <v>186</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>71</v>
@@ -3481,13 +3493,13 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3495,13 +3507,13 @@
         <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>71</v>
@@ -3511,27 +3523,27 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>71</v>
@@ -3541,57 +3553,57 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J47" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>71</v>
@@ -3601,7 +3613,7 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>80</v>
@@ -3612,13 +3624,13 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>56</v>
@@ -3631,24 +3643,24 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>203</v>
+        <v>59</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>56</v>
@@ -3661,54 +3673,54 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="J52" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>56</v>
@@ -3721,24 +3733,24 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>56</v>
@@ -3751,10 +3763,10 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="J54" s="3">
         <v>3</v>
@@ -3762,13 +3774,13 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>56</v>
@@ -3784,54 +3796,54 @@
         <v>216</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>71</v>
@@ -3841,54 +3853,54 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>226</v>
+        <v>157</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>56</v>
@@ -3896,62 +3908,64 @@
       <c r="E59" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="J60" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3961,27 +3975,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>71</v>
@@ -3991,57 +4005,57 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="J62" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>106</v>
+        <v>237</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C64" s="3" t="s">
-        <v>242</v>
+        <v>157</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -4051,57 +4065,57 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>71</v>
@@ -4111,30 +4125,30 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
@@ -4144,7 +4158,7 @@
         <v>251</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J67" s="3">
         <v>4</v>
@@ -4155,43 +4169,43 @@
         <v>252</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="J68" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>71</v>
@@ -4201,10 +4215,10 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="J69" s="3">
         <v>2</v>
@@ -4212,19 +4226,19 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>258</v>
+        <v>59</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>259</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
@@ -4242,59 +4256,59 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>141</v>
+        <v>261</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>59</v>
+        <v>264</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="J72" s="3">
         <v>3</v>
@@ -4302,13 +4316,13 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>265</v>
+        <v>59</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>56</v>
@@ -4321,60 +4335,60 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="J73" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>268</v>
+        <v>165</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>269</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>184</v>
+        <v>270</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>271</v>
+        <v>63</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
@@ -4384,10 +4398,10 @@
         <v>273</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -4395,13 +4409,13 @@
         <v>106</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>274</v>
+        <v>197</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>71</v>
@@ -4411,60 +4425,60 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="J76" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
@@ -4474,10 +4488,10 @@
         <v>280</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4488,7 +4502,7 @@
         <v>282</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>283</v>
+        <v>205</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>56</v>
@@ -4501,60 +4515,60 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>59</v>
+        <v>284</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>285</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>287</v>
+        <v>59</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>288</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
@@ -4564,51 +4578,51 @@
         <v>289</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="J81" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>292</v>
+        <v>226</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>116</v>
@@ -4621,27 +4635,27 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="C84" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>71</v>
@@ -4651,7 +4665,7 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>80</v>
@@ -4662,19 +4676,19 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>300</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
@@ -4684,24 +4698,24 @@
         <v>301</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>302</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>71</v>
@@ -4711,24 +4725,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="C87" s="3" t="s">
-        <v>152</v>
+        <v>286</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>116</v>
@@ -4741,27 +4755,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>309</v>
+        <v>182</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>71</v>
@@ -4771,27 +4785,27 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="J88" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>189</v>
+        <v>310</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>71</v>
@@ -4801,27 +4815,27 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="D90" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>71</v>
@@ -4831,24 +4845,24 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>316</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>303</v>
+        <v>170</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>116</v>
@@ -4864,7 +4878,7 @@
         <v>317</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="J91" s="3">
         <v>3</v>
@@ -4878,10 +4892,10 @@
         <v>319</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>283</v>
+        <v>152</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>71</v>
@@ -4894,66 +4908,64 @@
         <v>320</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>324</v>
-      </c>
       <c r="I93" s="3" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="D94" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>327</v>
+        <v>71</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>80</v>
@@ -4964,43 +4976,43 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>212</v>
+        <v>328</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>156</v>
+        <v>325</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J95" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>331</v>
+        <v>292</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>152</v>
+        <v>310</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>116</v>
@@ -5013,60 +5025,62 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J96" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="I97" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="J97" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="D98" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
@@ -5084,13 +5098,13 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>53</v>
+        <v>339</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>56</v>
@@ -5106,10 +5120,10 @@
         <v>340</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J99" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -5117,13 +5131,13 @@
         <v>341</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="D100" s="3" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>71</v>
@@ -5136,10 +5150,10 @@
         <v>343</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -5150,13 +5164,13 @@
         <v>345</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
@@ -5166,24 +5180,24 @@
         <v>346</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="J101" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>200</v>
+        <v>292</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>347</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>71</v>
@@ -5196,27 +5210,27 @@
         <v>348</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="J102" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
@@ -5240,13 +5254,13 @@
         <v>352</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>283</v>
+        <v>170</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
@@ -5256,27 +5270,27 @@
         <v>353</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="J104" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>59</v>
+        <v>292</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>156</v>
+        <v>336</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
@@ -5286,10 +5300,10 @@
         <v>354</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="J105" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -5300,13 +5314,13 @@
         <v>356</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
@@ -5316,7 +5330,7 @@
         <v>357</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="J106" s="3">
         <v>2</v>
@@ -5330,13 +5344,13 @@
         <v>359</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
@@ -5346,64 +5360,64 @@
         <v>360</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="J107" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="C108" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="J108" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>365</v>
-      </c>
       <c r="C109" s="3" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>80</v>
@@ -5414,13 +5428,13 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>365</v>
-      </c>
       <c r="C110" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>56</v>
@@ -5436,14 +5450,74 @@
         <v>368</v>
       </c>
       <c r="I110" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J110" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I111" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J110" s="3">
+      <c r="J111" s="3">
         <v>0</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J112" s="3">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J110"/>
+  <autoFilter ref="A1:J112"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5554,6 +5628,8 @@
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5561,7 +5637,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -5617,10 +5693,10 @@
         <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5628,7 +5704,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
@@ -5636,10 +5712,10 @@
         <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5647,18 +5723,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5666,18 +5742,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5685,18 +5761,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5704,18 +5780,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5723,18 +5799,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5742,18 +5818,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5761,18 +5837,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5780,18 +5856,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>106</v>
+        <v>240</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5799,18 +5875,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5818,18 +5894,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5837,18 +5913,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>156</v>
+        <v>298</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5856,18 +5932,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5875,18 +5951,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -5894,18 +5970,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5913,18 +5989,18 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -5932,18 +6008,18 @@
         <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -5951,18 +6027,18 @@
         <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -5970,18 +6046,18 @@
         <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -5989,18 +6065,18 @@
         <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -6008,18 +6084,18 @@
         <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -6027,18 +6103,18 @@
         <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -6046,11 +6122,30 @@
         <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>370</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G26"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6076,6 +6171,7 @@
     <hyperlink ref="G23" r:id="rId22"/>
     <hyperlink ref="G24" r:id="rId23"/>
     <hyperlink ref="G25" r:id="rId24"/>
+    <hyperlink ref="G26" r:id="rId25"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6089,23 +6185,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>227</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -6113,7 +6209,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B4" s="3">
         <v>19</v>
@@ -6121,7 +6217,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B5" s="3">
         <v>17</v>
@@ -6129,7 +6225,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -6137,7 +6233,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -6145,7 +6241,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -6153,7 +6249,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -6161,7 +6257,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -6169,7 +6265,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -6177,7 +6273,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -6185,7 +6281,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -6193,7 +6289,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -6201,7 +6297,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -6209,7 +6305,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -6222,7 +6318,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6231,7 +6327,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
@@ -6252,15 +6348,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>131</v>
+        <v>257</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6276,7 +6372,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6284,7 +6380,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6316,7 +6412,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6324,7 +6420,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6332,7 +6428,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6340,7 +6436,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6348,7 +6444,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>207</v>
+        <v>321</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6369,16 +6465,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
@@ -6442,13 +6538,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="C6" s="3">
-        <v>8.0</v>
+        <v>7.2</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6456,10 +6552,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3">
-        <v>7.2</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6470,10 +6566,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0</v>
+        <v>5.8</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6484,13 +6580,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>124</v>
+        <v>257</v>
       </c>
       <c r="C9" s="3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -6498,7 +6594,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C10" s="3">
         <v>4.2</v>
@@ -6512,7 +6608,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -6554,7 +6650,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6568,10 +6664,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6582,7 +6678,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6608,15 +6704,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6630,10 +6726,10 @@
         <v>71</v>
       </c>
       <c r="B3" s="3">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
@@ -6641,10 +6737,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -6663,7 +6759,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
@@ -6671,7 +6767,7 @@
         <v>56</v>
       </c>
       <c r="B2" s="3">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -6679,7 +6775,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -6687,12 +6783,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -6700,7 +6796,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="B6" s="3">
         <v>6</v>
@@ -6708,7 +6804,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6751,10 +6847,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6766,10 +6862,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6786,28 +6882,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6818,31 +6914,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>283</v>
+        <v>205</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4">
@@ -6850,31 +6946,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>331</v>
+        <v>409</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F4" s="3">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -6882,31 +6978,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>212</v>
+        <v>415</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>409</v>
+        <v>157</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="F5" s="3">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -6914,31 +7010,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>331</v>
+        <v>419</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>332</v>
+        <v>420</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>152</v>
+        <v>421</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>333</v>
+        <v>423</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -6946,31 +7042,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>414</v>
+        <v>201</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F7" s="3">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
@@ -6978,31 +7074,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F8" s="3">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -7010,31 +7106,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>331</v>
+        <v>430</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>272</v>
+        <v>431</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F9" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -7042,31 +7138,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>177</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -7074,28 +7170,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>428</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7106,28 +7202,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>434</v>
+        <v>205</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -7138,28 +7234,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>131</v>
+        <v>447</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>44</v>
@@ -7170,31 +7266,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
@@ -7202,28 +7298,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>453</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>44</v>
@@ -7234,28 +7330,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>44</v>
@@ -7266,31 +7362,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>195</v>
+        <v>461</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18">
@@ -7298,31 +7394,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>455</v>
+        <v>157</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F18" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -7330,31 +7426,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F19" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20">
@@ -7362,31 +7458,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F20" s="3">
         <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21">
@@ -7394,31 +7490,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>466</v>
+        <v>351</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
